--- a/research/traditional_assets/database/data/pakistan/pakistan_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_healthcare_support_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1805367099469659</v>
+        <v>0.1800451034881197</v>
       </c>
       <c r="C2">
-        <v>14.42307857468646</v>
+        <v>14.33256921181283</v>
       </c>
       <c r="D2">
-        <v>14.08807857468645</v>
+        <v>14.13966921181283</v>
       </c>
       <c r="E2">
-        <v>-1.51</v>
+        <v>-1.3679</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1421</v>
       </c>
       <c r="G2">
         <v>0.335</v>
@@ -1445,28 +1445,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.007147629999999999</v>
       </c>
       <c r="N2">
-        <v>0.5962499999999999</v>
+        <v>0.58910237</v>
       </c>
       <c r="O2">
-        <v>0.1729125</v>
+        <v>0.1708396873</v>
       </c>
       <c r="P2">
-        <v>0.4233375</v>
+        <v>0.4182626827</v>
       </c>
       <c r="Q2">
-        <v>0.4333375</v>
+        <v>0.4282626827</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1805367099469659</v>
+        <v>0.1815030035233532</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.8299426765982439</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>83.41925925096851</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1800451034881197</v>
+        <v>0.1795534970292735</v>
       </c>
       <c r="C3">
-        <v>14.33256921181283</v>
+        <v>14.24243908822626</v>
       </c>
       <c r="D3">
-        <v>14.13966921181283</v>
+        <v>14.19163908822626</v>
       </c>
       <c r="E3">
-        <v>-1.3679</v>
+        <v>-1.2258</v>
       </c>
       <c r="F3">
-        <v>0.1421</v>
+        <v>0.2842</v>
       </c>
       <c r="G3">
         <v>0.335</v>
@@ -1527,28 +1527,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M3">
-        <v>0.007147629999999999</v>
+        <v>0.01429526</v>
       </c>
       <c r="N3">
-        <v>0.58910237</v>
+        <v>0.5819547399999999</v>
       </c>
       <c r="O3">
-        <v>0.1708396873</v>
+        <v>0.1687668746</v>
       </c>
       <c r="P3">
-        <v>0.4182626827</v>
+        <v>0.4131878654</v>
       </c>
       <c r="Q3">
-        <v>0.4282626827</v>
+        <v>0.4231878654</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1815030035233532</v>
+        <v>0.1824890173768097</v>
       </c>
       <c r="T3">
-        <v>0.8299426765982439</v>
+        <v>0.8359730145823239</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>83.41925925096851</v>
+        <v>41.70962962548425</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1795534970292735</v>
+        <v>0.1790618905704273</v>
       </c>
       <c r="C4">
-        <v>14.24243908822626</v>
+        <v>14.1526924009965</v>
       </c>
       <c r="D4">
-        <v>14.19163908822626</v>
+        <v>14.2439924009965</v>
       </c>
       <c r="E4">
-        <v>-1.2258</v>
+        <v>-1.0837</v>
       </c>
       <c r="F4">
-        <v>0.2842</v>
+        <v>0.4263</v>
       </c>
       <c r="G4">
         <v>0.335</v>
@@ -1609,28 +1609,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M4">
-        <v>0.01429526</v>
+        <v>0.02144289</v>
       </c>
       <c r="N4">
-        <v>0.5819547399999999</v>
+        <v>0.57480711</v>
       </c>
       <c r="O4">
-        <v>0.1687668746</v>
+        <v>0.1666940619</v>
       </c>
       <c r="P4">
-        <v>0.4131878654</v>
+        <v>0.4081130481</v>
       </c>
       <c r="Q4">
-        <v>0.4231878654</v>
+        <v>0.4181130481</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1824890173768097</v>
+        <v>0.1834953614128117</v>
       </c>
       <c r="T4">
-        <v>0.8359730145823239</v>
+        <v>0.842127689432055</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>41.70962962548425</v>
+        <v>27.80641975032284</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1790618905704273</v>
+        <v>0.1785702841115811</v>
       </c>
       <c r="C5">
-        <v>14.1526924009965</v>
+        <v>14.06333340935498</v>
       </c>
       <c r="D5">
-        <v>14.2439924009965</v>
+        <v>14.29673340935498</v>
       </c>
       <c r="E5">
-        <v>-1.0837</v>
+        <v>-0.9416</v>
       </c>
       <c r="F5">
-        <v>0.4263</v>
+        <v>0.5684</v>
       </c>
       <c r="G5">
         <v>0.335</v>
@@ -1691,28 +1691,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M5">
-        <v>0.02144289</v>
+        <v>0.02859052</v>
       </c>
       <c r="N5">
-        <v>0.57480711</v>
+        <v>0.56765948</v>
       </c>
       <c r="O5">
-        <v>0.1666940619</v>
+        <v>0.1646212492</v>
       </c>
       <c r="P5">
-        <v>0.4081130481</v>
+        <v>0.4030382308</v>
       </c>
       <c r="Q5">
-        <v>0.4181130481</v>
+        <v>0.4130382308</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1834953614128117</v>
+        <v>0.1845226709495636</v>
       </c>
       <c r="T5">
-        <v>0.842127689432055</v>
+        <v>0.8484105866744885</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.80641975032284</v>
+        <v>20.85481481274213</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1785702841115811</v>
+        <v>0.1780786776527349</v>
       </c>
       <c r="C6">
-        <v>14.06333340935498</v>
+        <v>13.97436643584994</v>
       </c>
       <c r="D6">
-        <v>14.29673340935498</v>
+        <v>14.34986643584994</v>
       </c>
       <c r="E6">
-        <v>-0.9416</v>
+        <v>-0.7995</v>
       </c>
       <c r="F6">
-        <v>0.5684</v>
+        <v>0.7105</v>
       </c>
       <c r="G6">
         <v>0.335</v>
@@ -1773,28 +1773,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M6">
-        <v>0.02859052</v>
+        <v>0.03573815</v>
       </c>
       <c r="N6">
-        <v>0.56765948</v>
+        <v>0.5605118499999999</v>
       </c>
       <c r="O6">
-        <v>0.1646212492</v>
+        <v>0.1625484365</v>
       </c>
       <c r="P6">
-        <v>0.4030382308</v>
+        <v>0.3979634135</v>
       </c>
       <c r="Q6">
-        <v>0.4130382308</v>
+        <v>0.4079634135</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1845226709495636</v>
+        <v>0.1855716080555104</v>
       </c>
       <c r="T6">
-        <v>0.8484105866744885</v>
+        <v>0.8548257554378156</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.85481481274213</v>
+        <v>16.6838518501937</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1780786776527349</v>
+        <v>0.1775870711938887</v>
       </c>
       <c r="C7">
-        <v>13.97436643584994</v>
+        <v>13.88579586752739</v>
       </c>
       <c r="D7">
-        <v>14.34986643584994</v>
+        <v>14.40339586752739</v>
       </c>
       <c r="E7">
-        <v>-0.7995</v>
+        <v>-0.6574</v>
       </c>
       <c r="F7">
-        <v>0.7105</v>
+        <v>0.8526</v>
       </c>
       <c r="G7">
         <v>0.335</v>
@@ -1855,28 +1855,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M7">
-        <v>0.03573815</v>
+        <v>0.04288578</v>
       </c>
       <c r="N7">
-        <v>0.5605118499999999</v>
+        <v>0.55336422</v>
       </c>
       <c r="O7">
-        <v>0.1625484365</v>
+        <v>0.1604756238</v>
       </c>
       <c r="P7">
-        <v>0.3979634135</v>
+        <v>0.3928885962</v>
       </c>
       <c r="Q7">
-        <v>0.4079634135</v>
+        <v>0.4028885962</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1855716080555104</v>
+        <v>0.186642862972222</v>
       </c>
       <c r="T7">
-        <v>0.8548257554378156</v>
+        <v>0.861377417153554</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.6838518501937</v>
+        <v>13.90320987516142</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1775870711938887</v>
+        <v>0.1771700147350425</v>
       </c>
       <c r="C8">
-        <v>13.88579586752739</v>
+        <v>13.78942189783945</v>
       </c>
       <c r="D8">
-        <v>14.40339586752739</v>
+        <v>14.44912189783945</v>
       </c>
       <c r="E8">
-        <v>-0.6574000000000001</v>
+        <v>-0.5153000000000002</v>
       </c>
       <c r="F8">
-        <v>0.8525999999999999</v>
+        <v>0.9946999999999998</v>
       </c>
       <c r="G8">
         <v>0.335</v>
@@ -1937,45 +1937,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M8">
-        <v>0.04288577999999999</v>
+        <v>0.05152545999999999</v>
       </c>
       <c r="N8">
-        <v>0.55336422</v>
+        <v>0.5447245399999999</v>
       </c>
       <c r="O8">
-        <v>0.1604756238</v>
+        <v>0.1579701166</v>
       </c>
       <c r="P8">
-        <v>0.3928885962</v>
+        <v>0.3867544234</v>
       </c>
       <c r="Q8">
-        <v>0.4028885962</v>
+        <v>0.3967544234</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.186642862972222</v>
+        <v>0.187737155629078</v>
       </c>
       <c r="T8">
-        <v>0.861377417153554</v>
+        <v>0.8680699748201683</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.29</v>
       </c>
       <c r="W8">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.90320987516142</v>
+        <v>11.571949090799</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1771700147350425</v>
+        <v>0.1766890582761963</v>
       </c>
       <c r="C9">
-        <v>13.78942189783945</v>
+        <v>13.70041570562557</v>
       </c>
       <c r="D9">
-        <v>14.44912189783945</v>
+        <v>14.50221570562556</v>
       </c>
       <c r="E9">
-        <v>-0.5153</v>
+        <v>-0.3732</v>
       </c>
       <c r="F9">
-        <v>0.9947</v>
+        <v>1.1368</v>
       </c>
       <c r="G9">
         <v>0.335</v>
@@ -2019,28 +2019,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M9">
-        <v>0.05152546</v>
+        <v>0.05888624</v>
       </c>
       <c r="N9">
-        <v>0.5447245399999999</v>
+        <v>0.53736376</v>
       </c>
       <c r="O9">
-        <v>0.1579701166</v>
+        <v>0.1558354904</v>
       </c>
       <c r="P9">
-        <v>0.3867544234</v>
+        <v>0.3815282696</v>
       </c>
       <c r="Q9">
-        <v>0.3967544234</v>
+        <v>0.3915282696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.187737155629078</v>
+        <v>0.1888552372567351</v>
       </c>
       <c r="T9">
-        <v>0.8680699748201683</v>
+        <v>0.8749080228708395</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.57194909079899</v>
+        <v>10.12545545444912</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1766890582761963</v>
+        <v>0.1763167318173501</v>
       </c>
       <c r="C10">
-        <v>13.70041570562557</v>
+        <v>13.59968632948286</v>
       </c>
       <c r="D10">
-        <v>14.50221570562556</v>
+        <v>14.54358632948286</v>
       </c>
       <c r="E10">
-        <v>-0.3732</v>
+        <v>-0.2311000000000001</v>
       </c>
       <c r="F10">
-        <v>1.1368</v>
+        <v>1.2789</v>
       </c>
       <c r="G10">
         <v>0.335</v>
@@ -2101,45 +2101,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M10">
-        <v>0.05888624</v>
+        <v>0.06842115</v>
       </c>
       <c r="N10">
-        <v>0.53736376</v>
+        <v>0.5278288499999999</v>
       </c>
       <c r="O10">
-        <v>0.1558354904</v>
+        <v>0.1530703665</v>
       </c>
       <c r="P10">
-        <v>0.3815282696</v>
+        <v>0.3747584835</v>
       </c>
       <c r="Q10">
-        <v>0.3915282696</v>
+        <v>0.3847584835</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1888552372567351</v>
+        <v>0.1899978921069781</v>
       </c>
       <c r="T10">
-        <v>0.8749080228708395</v>
+        <v>0.8818963576918551</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.29</v>
       </c>
       <c r="W10">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.12545545444912</v>
+        <v>8.714410675646345</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1763167318173501</v>
+        <v>0.1758478453585039</v>
       </c>
       <c r="C11">
-        <v>13.59968632948286</v>
+        <v>13.51002311283869</v>
       </c>
       <c r="D11">
-        <v>14.54358632948286</v>
+        <v>14.59602311283868</v>
       </c>
       <c r="E11">
-        <v>-0.2311000000000001</v>
+        <v>-0.08900000000000019</v>
       </c>
       <c r="F11">
-        <v>1.2789</v>
+        <v>1.421</v>
       </c>
       <c r="G11">
         <v>0.335</v>
@@ -2183,28 +2183,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M11">
-        <v>0.06842115</v>
+        <v>0.07602349999999999</v>
       </c>
       <c r="N11">
-        <v>0.5278288499999999</v>
+        <v>0.5202264999999999</v>
       </c>
       <c r="O11">
-        <v>0.1530703665</v>
+        <v>0.150865685</v>
       </c>
       <c r="P11">
-        <v>0.3747584835</v>
+        <v>0.369360815</v>
       </c>
       <c r="Q11">
-        <v>0.3847584835</v>
+        <v>0.379360815</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1899978921069781</v>
+        <v>0.1911659392872265</v>
       </c>
       <c r="T11">
-        <v>0.8818963576918551</v>
+        <v>0.8890399888422267</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.714410675646345</v>
+        <v>7.842969608081711</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1758478453585039</v>
+        <v>0.1754414388996577</v>
       </c>
       <c r="C12">
-        <v>13.51002311283869</v>
+        <v>13.41367945523101</v>
       </c>
       <c r="D12">
-        <v>14.59602311283868</v>
+        <v>14.641779455231</v>
       </c>
       <c r="E12">
-        <v>-0.08899999999999997</v>
+        <v>0.05309999999999993</v>
       </c>
       <c r="F12">
-        <v>1.421</v>
+        <v>1.5631</v>
       </c>
       <c r="G12">
         <v>0.335</v>
@@ -2265,45 +2265,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M12">
-        <v>0.07602349999999999</v>
+        <v>0.08487633</v>
       </c>
       <c r="N12">
-        <v>0.5202264999999999</v>
+        <v>0.51137367</v>
       </c>
       <c r="O12">
-        <v>0.150865685</v>
+        <v>0.1482983643</v>
       </c>
       <c r="P12">
-        <v>0.369360815</v>
+        <v>0.3630753057</v>
       </c>
       <c r="Q12">
-        <v>0.379360815</v>
+        <v>0.3730753057</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1911659392872265</v>
+        <v>0.1923602347187165</v>
       </c>
       <c r="T12">
-        <v>0.8890399888422267</v>
+        <v>0.8963441510296853</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.29</v>
       </c>
       <c r="W12">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.842969608081711</v>
+        <v>7.024926737525056</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1754414388996577</v>
+        <v>0.1749782324408115</v>
       </c>
       <c r="C13">
-        <v>13.41367945523101</v>
+        <v>13.32408185199334</v>
       </c>
       <c r="D13">
-        <v>14.641779455231</v>
+        <v>14.69428185199334</v>
       </c>
       <c r="E13">
-        <v>0.05309999999999993</v>
+        <v>0.1951999999999998</v>
       </c>
       <c r="F13">
-        <v>1.5631</v>
+        <v>1.7052</v>
       </c>
       <c r="G13">
         <v>0.335</v>
@@ -2347,28 +2347,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M13">
-        <v>0.08487633</v>
+        <v>0.09259236</v>
       </c>
       <c r="N13">
-        <v>0.51137367</v>
+        <v>0.5036576399999999</v>
       </c>
       <c r="O13">
-        <v>0.1482983643</v>
+        <v>0.1460607156</v>
       </c>
       <c r="P13">
-        <v>0.3630753057</v>
+        <v>0.3575969243999999</v>
       </c>
       <c r="Q13">
-        <v>0.3730753057</v>
+        <v>0.3675969243999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1923602347187165</v>
+        <v>0.1935816732281949</v>
       </c>
       <c r="T13">
-        <v>0.8963441510296853</v>
+        <v>0.9038143169032224</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.024926737525056</v>
+        <v>6.439516176064633</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1749782324408115</v>
+        <v>0.1746073259819653</v>
       </c>
       <c r="C14">
-        <v>13.32408185199334</v>
+        <v>13.22429469410431</v>
       </c>
       <c r="D14">
-        <v>14.69428185199334</v>
+        <v>14.7365946941043</v>
       </c>
       <c r="E14">
-        <v>0.1951999999999998</v>
+        <v>0.3372999999999999</v>
       </c>
       <c r="F14">
-        <v>1.7052</v>
+        <v>1.8473</v>
       </c>
       <c r="G14">
         <v>0.335</v>
@@ -2429,45 +2429,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M14">
-        <v>0.09259236</v>
+        <v>0.10215569</v>
       </c>
       <c r="N14">
-        <v>0.5036576399999999</v>
+        <v>0.4940943099999999</v>
       </c>
       <c r="O14">
-        <v>0.1460607156</v>
+        <v>0.1432873499</v>
       </c>
       <c r="P14">
-        <v>0.3575969243999999</v>
+        <v>0.3508069601</v>
       </c>
       <c r="Q14">
-        <v>0.3675969243999999</v>
+        <v>0.3608069601</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1935816732281949</v>
+        <v>0.1948311907838682</v>
       </c>
       <c r="T14">
-        <v>0.9038143169032224</v>
+        <v>0.9114562107278755</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.29</v>
       </c>
       <c r="W14">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.439516176064633</v>
+        <v>5.8366792882511</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1746073259819653</v>
+        <v>0.1741512195231191</v>
       </c>
       <c r="C15">
-        <v>13.22429469410431</v>
+        <v>13.1345623774528</v>
       </c>
       <c r="D15">
-        <v>14.7365946941043</v>
+        <v>14.7889623774528</v>
       </c>
       <c r="E15">
-        <v>0.3372999999999999</v>
+        <v>0.4794</v>
       </c>
       <c r="F15">
-        <v>1.8473</v>
+        <v>1.9894</v>
       </c>
       <c r="G15">
         <v>0.335</v>
@@ -2511,28 +2511,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M15">
-        <v>0.10215569</v>
+        <v>0.11001382</v>
       </c>
       <c r="N15">
-        <v>0.4940943099999999</v>
+        <v>0.4862361799999999</v>
       </c>
       <c r="O15">
-        <v>0.1432873499</v>
+        <v>0.1410084922</v>
       </c>
       <c r="P15">
-        <v>0.3508069601</v>
+        <v>0.3452276877999999</v>
       </c>
       <c r="Q15">
-        <v>0.3608069601</v>
+        <v>0.3552276877999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1948311907838682</v>
+        <v>0.1961097668873478</v>
       </c>
       <c r="T15">
-        <v>0.9114562107278755</v>
+        <v>0.9192758230135668</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.8366792882511</v>
+        <v>5.419773624804591</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1741512195231191</v>
+        <v>0.1736951130642729</v>
       </c>
       <c r="C16">
-        <v>13.1345623774528</v>
+        <v>13.04520357372197</v>
       </c>
       <c r="D16">
-        <v>14.7889623774528</v>
+        <v>14.84170357372197</v>
       </c>
       <c r="E16">
-        <v>0.4794</v>
+        <v>0.6215000000000004</v>
       </c>
       <c r="F16">
-        <v>1.9894</v>
+        <v>2.1315</v>
       </c>
       <c r="G16">
         <v>0.335</v>
@@ -2593,28 +2593,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M16">
-        <v>0.11001382</v>
+        <v>0.11787195</v>
       </c>
       <c r="N16">
-        <v>0.4862361799999999</v>
+        <v>0.4783780499999999</v>
       </c>
       <c r="O16">
-        <v>0.1410084922</v>
+        <v>0.1387296344999999</v>
       </c>
       <c r="P16">
-        <v>0.3452276877999999</v>
+        <v>0.3396484154999999</v>
       </c>
       <c r="Q16">
-        <v>0.3552276877999999</v>
+        <v>0.3496484154999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1961097668873478</v>
+        <v>0.1974184271344387</v>
       </c>
       <c r="T16">
-        <v>0.9192758230135668</v>
+        <v>0.9272794261765687</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.419773624804591</v>
+        <v>5.058455383150951</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1736951130642729</v>
+        <v>0.1732390066054267</v>
       </c>
       <c r="C17">
-        <v>13.04520357372197</v>
+        <v>12.95622229333986</v>
       </c>
       <c r="D17">
-        <v>14.84170357372197</v>
+        <v>14.89482229333986</v>
       </c>
       <c r="E17">
-        <v>0.6214999999999999</v>
+        <v>0.7636000000000001</v>
       </c>
       <c r="F17">
-        <v>2.1315</v>
+        <v>2.2736</v>
       </c>
       <c r="G17">
         <v>0.335</v>
@@ -2675,28 +2675,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M17">
-        <v>0.11787195</v>
+        <v>0.12573008</v>
       </c>
       <c r="N17">
-        <v>0.4783780499999999</v>
+        <v>0.4705199199999999</v>
       </c>
       <c r="O17">
-        <v>0.1387296345</v>
+        <v>0.1364507768</v>
       </c>
       <c r="P17">
-        <v>0.3396484155</v>
+        <v>0.3340691431999999</v>
       </c>
       <c r="Q17">
-        <v>0.3496484155</v>
+        <v>0.3440691431999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1974184271344387</v>
+        <v>0.1987582459588413</v>
       </c>
       <c r="T17">
-        <v>0.9272794261765687</v>
+        <v>0.9354735913196418</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.058455383150952</v>
+        <v>4.742301921704017</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1732390066054267</v>
+        <v>0.1730846501465805</v>
       </c>
       <c r="C18">
-        <v>12.95622229333986</v>
+        <v>12.83218505284538</v>
       </c>
       <c r="D18">
-        <v>14.89482229333986</v>
+        <v>14.91288505284538</v>
       </c>
       <c r="E18">
-        <v>0.7636000000000001</v>
+        <v>0.9057000000000002</v>
       </c>
       <c r="F18">
-        <v>2.2736</v>
+        <v>2.4157</v>
       </c>
       <c r="G18">
         <v>0.335</v>
@@ -2757,45 +2757,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M18">
-        <v>0.12573008</v>
+        <v>0.13962746</v>
       </c>
       <c r="N18">
-        <v>0.4705199199999999</v>
+        <v>0.4566225399999999</v>
       </c>
       <c r="O18">
-        <v>0.1364507768</v>
+        <v>0.1324205366</v>
       </c>
       <c r="P18">
-        <v>0.3340691431999999</v>
+        <v>0.3242020033999999</v>
       </c>
       <c r="Q18">
-        <v>0.3440691431999999</v>
+        <v>0.3342020033999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1987582459588413</v>
+        <v>0.2001303495741934</v>
       </c>
       <c r="T18">
-        <v>0.9354735913196418</v>
+        <v>0.9438652062251989</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.29</v>
       </c>
       <c r="W18">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.742301921704017</v>
+        <v>4.270291817956152</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1730846501465805</v>
+        <v>0.1726462936877343</v>
       </c>
       <c r="C19">
-        <v>12.83218505284538</v>
+        <v>12.74162112294167</v>
       </c>
       <c r="D19">
-        <v>14.91288505284538</v>
+        <v>14.96442112294167</v>
       </c>
       <c r="E19">
-        <v>0.9057000000000002</v>
+        <v>1.0478</v>
       </c>
       <c r="F19">
-        <v>2.4157</v>
+        <v>2.5578</v>
       </c>
       <c r="G19">
         <v>0.335</v>
@@ -2839,28 +2839,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M19">
-        <v>0.13962746</v>
+        <v>0.14784084</v>
       </c>
       <c r="N19">
-        <v>0.4566225399999999</v>
+        <v>0.4484091599999999</v>
       </c>
       <c r="O19">
-        <v>0.1324205366</v>
+        <v>0.1300386564</v>
       </c>
       <c r="P19">
-        <v>0.3242020033999999</v>
+        <v>0.3183705036</v>
       </c>
       <c r="Q19">
-        <v>0.3342020033999999</v>
+        <v>0.3283705036</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2001303495741934</v>
+        <v>0.2015359191313833</v>
       </c>
       <c r="T19">
-        <v>0.9438652062251989</v>
+        <v>0.9524614946650376</v>
       </c>
       <c r="U19">
         <v>0.0578</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.270291817956152</v>
+        <v>4.033053383625254</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1726462936877343</v>
+        <v>0.1726800872288881</v>
       </c>
       <c r="C20">
-        <v>12.74162112294167</v>
+        <v>12.59553546378817</v>
       </c>
       <c r="D20">
-        <v>14.96442112294167</v>
+        <v>14.96043546378817</v>
       </c>
       <c r="E20">
-        <v>1.0478</v>
+        <v>1.1899</v>
       </c>
       <c r="F20">
-        <v>2.5578</v>
+        <v>2.6999</v>
       </c>
       <c r="G20">
         <v>0.335</v>
@@ -2921,45 +2921,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M20">
-        <v>0.14784084</v>
+        <v>0.16550387</v>
       </c>
       <c r="N20">
-        <v>0.44840916</v>
+        <v>0.4307461299999999</v>
       </c>
       <c r="O20">
-        <v>0.1300386564</v>
+        <v>0.1249163777</v>
       </c>
       <c r="P20">
-        <v>0.3183705036</v>
+        <v>0.3058297523</v>
       </c>
       <c r="Q20">
-        <v>0.3283705036</v>
+        <v>0.3158297523</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2015359191313833</v>
+        <v>0.2029761941097384</v>
       </c>
       <c r="T20">
-        <v>0.9524614946650376</v>
+        <v>0.961270037140428</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.29</v>
       </c>
       <c r="W20">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.033053383625255</v>
+        <v>3.602634790352636</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1726800872288881</v>
+        <v>0.1726641807700419</v>
       </c>
       <c r="C21">
-        <v>12.59553546378817</v>
+        <v>12.45531123005712</v>
       </c>
       <c r="D21">
-        <v>14.96043546378817</v>
+        <v>14.96231123005712</v>
       </c>
       <c r="E21">
-        <v>1.1899</v>
+        <v>1.332</v>
       </c>
       <c r="F21">
-        <v>2.6999</v>
+        <v>2.842</v>
       </c>
       <c r="G21">
         <v>0.335</v>
@@ -3003,45 +3003,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M21">
-        <v>0.16550387</v>
+        <v>0.1821722</v>
       </c>
       <c r="N21">
-        <v>0.4307461299999999</v>
+        <v>0.4140777999999999</v>
       </c>
       <c r="O21">
-        <v>0.1249163777</v>
+        <v>0.120082562</v>
       </c>
       <c r="P21">
-        <v>0.3058297523</v>
+        <v>0.2939952379999999</v>
       </c>
       <c r="Q21">
-        <v>0.3158297523</v>
+        <v>0.3039952379999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2029761941097384</v>
+        <v>0.2044524759625523</v>
       </c>
       <c r="T21">
-        <v>0.961270037140428</v>
+        <v>0.9702987931777032</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.29</v>
       </c>
       <c r="W21">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.602634790352636</v>
+        <v>3.273002137537999</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1726641807700419</v>
+        <v>0.1722705543111957</v>
       </c>
       <c r="C22">
-        <v>12.45531123005712</v>
+        <v>12.35977986903968</v>
       </c>
       <c r="D22">
-        <v>14.96231123005712</v>
+        <v>15.00887986903967</v>
       </c>
       <c r="E22">
-        <v>1.332</v>
+        <v>1.4741</v>
       </c>
       <c r="F22">
-        <v>2.842</v>
+        <v>2.9841</v>
       </c>
       <c r="G22">
         <v>0.335</v>
@@ -3085,28 +3085,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M22">
-        <v>0.1821722</v>
+        <v>0.19128081</v>
       </c>
       <c r="N22">
-        <v>0.4140777999999999</v>
+        <v>0.4049691899999999</v>
       </c>
       <c r="O22">
-        <v>0.120082562</v>
+        <v>0.1174410651</v>
       </c>
       <c r="P22">
-        <v>0.2939952379999999</v>
+        <v>0.2875281249</v>
       </c>
       <c r="Q22">
-        <v>0.3039952379999999</v>
+        <v>0.2975281249</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2044524759625523</v>
+        <v>0.2059661320394882</v>
       </c>
       <c r="T22">
-        <v>0.9702987931777032</v>
+        <v>0.9795561253171878</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.273002137537999</v>
+        <v>3.117144892893332</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1722705543111957</v>
+        <v>0.1730952878523495</v>
       </c>
       <c r="C23">
-        <v>12.35977986903968</v>
+        <v>12.12043882538453</v>
       </c>
       <c r="D23">
-        <v>15.00887986903967</v>
+        <v>14.91163882538453</v>
       </c>
       <c r="E23">
-        <v>1.4741</v>
+        <v>1.6162</v>
       </c>
       <c r="F23">
-        <v>2.9841</v>
+        <v>3.1262</v>
       </c>
       <c r="G23">
         <v>0.335</v>
@@ -3167,45 +3167,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M23">
-        <v>0.19128081</v>
+        <v>0.22477378</v>
       </c>
       <c r="N23">
-        <v>0.40496919</v>
+        <v>0.3714762199999999</v>
       </c>
       <c r="O23">
-        <v>0.1174410651</v>
+        <v>0.1077281038</v>
       </c>
       <c r="P23">
-        <v>0.2875281249</v>
+        <v>0.2637481161999999</v>
       </c>
       <c r="Q23">
-        <v>0.2975281249</v>
+        <v>0.2737481161999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2059661320394882</v>
+        <v>0.2075185998107044</v>
       </c>
       <c r="T23">
-        <v>0.9795561253171878</v>
+        <v>0.9890508249474285</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.29</v>
       </c>
       <c r="W23">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.117144892893333</v>
+        <v>2.652667050400629</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1730952878523495</v>
+        <v>0.1727570413935033</v>
       </c>
       <c r="C24">
-        <v>12.12043882538453</v>
+        <v>12.01806729552622</v>
       </c>
       <c r="D24">
-        <v>14.91163882538453</v>
+        <v>14.95136729552622</v>
       </c>
       <c r="E24">
-        <v>1.6162</v>
+        <v>1.7583</v>
       </c>
       <c r="F24">
-        <v>3.1262</v>
+        <v>3.2683</v>
       </c>
       <c r="G24">
         <v>0.335</v>
@@ -3249,28 +3249,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M24">
-        <v>0.22477378</v>
+        <v>0.23499077</v>
       </c>
       <c r="N24">
-        <v>0.3714762199999999</v>
+        <v>0.3612592299999999</v>
       </c>
       <c r="O24">
-        <v>0.1077281038</v>
+        <v>0.1047651767</v>
       </c>
       <c r="P24">
-        <v>0.2637481161999999</v>
+        <v>0.2564940533</v>
       </c>
       <c r="Q24">
-        <v>0.2737481161999999</v>
+        <v>0.2664940533</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2075185998107044</v>
+        <v>0.2091113914201342</v>
       </c>
       <c r="T24">
-        <v>0.9890508249474285</v>
+        <v>0.9987921401524807</v>
       </c>
       <c r="U24">
         <v>0.07190000000000001</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.652667050400629</v>
+        <v>2.53733370038321</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1727570413935033</v>
+        <v>0.1730833549346571</v>
       </c>
       <c r="C25">
-        <v>12.01806729552622</v>
+        <v>11.83763680361077</v>
       </c>
       <c r="D25">
-        <v>14.95136729552622</v>
+        <v>14.91303680361077</v>
       </c>
       <c r="E25">
-        <v>1.7583</v>
+        <v>1.9004</v>
       </c>
       <c r="F25">
-        <v>3.2683</v>
+        <v>3.4104</v>
       </c>
       <c r="G25">
         <v>0.335</v>
@@ -3331,45 +3331,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M25">
-        <v>0.23499077</v>
+        <v>0.25850832</v>
       </c>
       <c r="N25">
-        <v>0.3612592299999999</v>
+        <v>0.3377416799999999</v>
       </c>
       <c r="O25">
-        <v>0.1047651767</v>
+        <v>0.09794508719999998</v>
       </c>
       <c r="P25">
-        <v>0.2564940533</v>
+        <v>0.2397965928</v>
       </c>
       <c r="Q25">
-        <v>0.2664940533</v>
+        <v>0.2497965928</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2091113914201342</v>
+        <v>0.210746098598233</v>
       </c>
       <c r="T25">
-        <v>0.9987921401524807</v>
+        <v>1.008789805757666</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.29</v>
       </c>
       <c r="W25">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.53733370038321</v>
+        <v>2.306502165965103</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1730833549346571</v>
+        <v>0.1727727984758109</v>
       </c>
       <c r="C26">
-        <v>11.83763680361077</v>
+        <v>11.73201185933899</v>
       </c>
       <c r="D26">
-        <v>14.91303680361077</v>
+        <v>14.94951185933899</v>
       </c>
       <c r="E26">
-        <v>1.9004</v>
+        <v>2.0425</v>
       </c>
       <c r="F26">
-        <v>3.4104</v>
+        <v>3.5525</v>
       </c>
       <c r="G26">
         <v>0.335</v>
@@ -3413,28 +3413,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M26">
-        <v>0.25850832</v>
+        <v>0.2692795</v>
       </c>
       <c r="N26">
-        <v>0.3377416799999999</v>
+        <v>0.3269704999999999</v>
       </c>
       <c r="O26">
-        <v>0.09794508719999998</v>
+        <v>0.09482144499999998</v>
       </c>
       <c r="P26">
-        <v>0.2397965928</v>
+        <v>0.232149055</v>
       </c>
       <c r="Q26">
-        <v>0.2497965928</v>
+        <v>0.242149055</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.210746098598233</v>
+        <v>0.2124243979677478</v>
       </c>
       <c r="T26">
-        <v>1.008789805757666</v>
+        <v>1.019054075778989</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.306502165965103</v>
+        <v>2.214242079326499</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1727727984758109</v>
+        <v>0.1724622420169647</v>
       </c>
       <c r="C27">
-        <v>11.73201185933899</v>
+        <v>11.62656577759107</v>
       </c>
       <c r="D27">
-        <v>14.94951185933899</v>
+        <v>14.98616577759107</v>
       </c>
       <c r="E27">
-        <v>2.0425</v>
+        <v>2.1846</v>
       </c>
       <c r="F27">
-        <v>3.5525</v>
+        <v>3.6946</v>
       </c>
       <c r="G27">
         <v>0.335</v>
@@ -3495,28 +3495,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M27">
-        <v>0.2692795</v>
+        <v>0.28005068</v>
       </c>
       <c r="N27">
-        <v>0.3269704999999999</v>
+        <v>0.31619932</v>
       </c>
       <c r="O27">
-        <v>0.09482144499999998</v>
+        <v>0.09169780279999998</v>
       </c>
       <c r="P27">
-        <v>0.232149055</v>
+        <v>0.2245015172</v>
       </c>
       <c r="Q27">
-        <v>0.242149055</v>
+        <v>0.2345015172</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2124243979677478</v>
+        <v>0.214148056779682</v>
       </c>
       <c r="T27">
-        <v>1.019054075778989</v>
+        <v>1.029595758503592</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.214242079326499</v>
+        <v>2.129078922429326</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1724622420169647</v>
+        <v>0.1721516855581185</v>
       </c>
       <c r="C28">
-        <v>11.62656577759107</v>
+        <v>11.5212998772314</v>
       </c>
       <c r="D28">
-        <v>14.98616577759107</v>
+        <v>15.0229998772314</v>
       </c>
       <c r="E28">
-        <v>2.1846</v>
+        <v>2.3267</v>
       </c>
       <c r="F28">
-        <v>3.6946</v>
+        <v>3.8367</v>
       </c>
       <c r="G28">
         <v>0.335</v>
@@ -3577,28 +3577,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M28">
-        <v>0.28005068</v>
+        <v>0.29082186</v>
       </c>
       <c r="N28">
-        <v>0.31619932</v>
+        <v>0.3054281399999999</v>
       </c>
       <c r="O28">
-        <v>0.09169780279999998</v>
+        <v>0.08857416059999997</v>
       </c>
       <c r="P28">
-        <v>0.2245015172</v>
+        <v>0.2168539794</v>
       </c>
       <c r="Q28">
-        <v>0.2345015172</v>
+        <v>0.2268539794</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.214148056779682</v>
+        <v>0.2159189391207102</v>
       </c>
       <c r="T28">
-        <v>1.029595758503592</v>
+        <v>1.040426254453525</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.129078922429326</v>
+        <v>2.050224147524536</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1721516855581185</v>
+        <v>0.1746640890992723</v>
       </c>
       <c r="C29">
-        <v>11.5212998772314</v>
+        <v>11.08630339727232</v>
       </c>
       <c r="D29">
-        <v>15.0229998772314</v>
+        <v>14.73010339727232</v>
       </c>
       <c r="E29">
-        <v>2.3267</v>
+        <v>2.4688</v>
       </c>
       <c r="F29">
-        <v>3.8367</v>
+        <v>3.9788</v>
       </c>
       <c r="G29">
         <v>0.335</v>
@@ -3659,45 +3659,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M29">
-        <v>0.29082186</v>
+        <v>0.358092</v>
       </c>
       <c r="N29">
-        <v>0.3054281399999999</v>
+        <v>0.2381579999999999</v>
       </c>
       <c r="O29">
-        <v>0.08857416059999997</v>
+        <v>0.06906581999999997</v>
       </c>
       <c r="P29">
-        <v>0.2168539794</v>
+        <v>0.16909218</v>
       </c>
       <c r="Q29">
-        <v>0.2268539794</v>
+        <v>0.17909218</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2159189391207102</v>
+        <v>0.2177390126378782</v>
       </c>
       <c r="T29">
-        <v>1.040426254453525</v>
+        <v>1.05155759751318</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.29</v>
       </c>
       <c r="W29">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.050224147524536</v>
+        <v>1.665074896953855</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1746640890992723</v>
+        <v>0.1744543526404261</v>
       </c>
       <c r="C30">
-        <v>11.08630339727232</v>
+        <v>10.96821688505238</v>
       </c>
       <c r="D30">
-        <v>14.73010339727232</v>
+        <v>14.75411688505238</v>
       </c>
       <c r="E30">
-        <v>2.4688</v>
+        <v>2.610900000000001</v>
       </c>
       <c r="F30">
-        <v>3.9788</v>
+        <v>4.120900000000001</v>
       </c>
       <c r="G30">
         <v>0.335</v>
@@ -3741,28 +3741,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M30">
-        <v>0.358092</v>
+        <v>0.3708810000000001</v>
       </c>
       <c r="N30">
-        <v>0.2381579999999999</v>
+        <v>0.2253689999999999</v>
       </c>
       <c r="O30">
-        <v>0.06906581999999997</v>
+        <v>0.06535700999999997</v>
       </c>
       <c r="P30">
-        <v>0.16909218</v>
+        <v>0.1600119899999999</v>
       </c>
       <c r="Q30">
-        <v>0.17909218</v>
+        <v>0.1700119899999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2177390126378782</v>
+        <v>0.219610355831586</v>
       </c>
       <c r="T30">
-        <v>1.05155759751318</v>
+        <v>1.063002499532261</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.665074896953855</v>
+        <v>1.607658521196826</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1744543526404261</v>
+        <v>0.1742446161815799</v>
       </c>
       <c r="C31">
-        <v>10.96821688505239</v>
+        <v>10.85020879579857</v>
       </c>
       <c r="D31">
-        <v>14.75411688505238</v>
+        <v>14.77820879579856</v>
       </c>
       <c r="E31">
-        <v>2.6109</v>
+        <v>2.753</v>
       </c>
       <c r="F31">
-        <v>4.1209</v>
+        <v>4.263</v>
       </c>
       <c r="G31">
         <v>0.335</v>
@@ -3823,28 +3823,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M31">
-        <v>0.370881</v>
+        <v>0.38367</v>
       </c>
       <c r="N31">
-        <v>0.225369</v>
+        <v>0.21258</v>
       </c>
       <c r="O31">
-        <v>0.06535700999999999</v>
+        <v>0.06164819999999999</v>
       </c>
       <c r="P31">
-        <v>0.16001199</v>
+        <v>0.1509318</v>
       </c>
       <c r="Q31">
-        <v>0.17001199</v>
+        <v>0.1609318</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.219610355831586</v>
+        <v>0.2215351659736855</v>
       </c>
       <c r="T31">
-        <v>1.063002499532261</v>
+        <v>1.074774398751887</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.607658521196826</v>
+        <v>1.554069903823598</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1742446161815799</v>
+        <v>0.1740348797227337</v>
       </c>
       <c r="C32">
-        <v>10.85020879579857</v>
+        <v>10.7322795143084</v>
       </c>
       <c r="D32">
-        <v>14.77820879579856</v>
+        <v>14.8023795143084</v>
       </c>
       <c r="E32">
-        <v>2.753</v>
+        <v>2.8951</v>
       </c>
       <c r="F32">
-        <v>4.263</v>
+        <v>4.4051</v>
       </c>
       <c r="G32">
         <v>0.335</v>
@@ -3905,28 +3905,28 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M32">
-        <v>0.38367</v>
+        <v>0.396459</v>
       </c>
       <c r="N32">
-        <v>0.21258</v>
+        <v>0.1997909999999999</v>
       </c>
       <c r="O32">
-        <v>0.06164819999999999</v>
+        <v>0.05793938999999998</v>
       </c>
       <c r="P32">
-        <v>0.1509318</v>
+        <v>0.14185161</v>
       </c>
       <c r="Q32">
-        <v>0.1609318</v>
+        <v>0.15185161</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2215351659736855</v>
+        <v>0.2235157677141068</v>
       </c>
       <c r="T32">
-        <v>1.074774398751887</v>
+        <v>1.086887512441648</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.554069903823598</v>
+        <v>1.503938616603482</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1740348797227337</v>
+        <v>0.1895199108442191</v>
       </c>
       <c r="C33">
-        <v>10.7322795143084</v>
+        <v>8.995304412419729</v>
       </c>
       <c r="D33">
-        <v>14.8023795143084</v>
+        <v>13.20750441241973</v>
       </c>
       <c r="E33">
-        <v>2.8951</v>
+        <v>3.0372</v>
       </c>
       <c r="F33">
-        <v>4.4051</v>
+        <v>4.5472</v>
       </c>
       <c r="G33">
         <v>0.335</v>
@@ -3987,45 +3987,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M33">
-        <v>0.396459</v>
+        <v>0.6675289600000001</v>
       </c>
       <c r="N33">
-        <v>0.1997909999999999</v>
+        <v>-0.07127896000000011</v>
       </c>
       <c r="O33">
-        <v>0.05793938999999998</v>
+        <v>-0.02067089840000003</v>
       </c>
       <c r="P33">
-        <v>0.14185161</v>
+        <v>-0.05060806160000008</v>
       </c>
       <c r="Q33">
-        <v>0.15185161</v>
+        <v>-0.04060806160000007</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2235157677141068</v>
+        <v>0.2275180561634675</v>
       </c>
       <c r="T33">
-        <v>1.086887512441648</v>
+        <v>1.111365010374175</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.29</v>
+        <v>0.2590337054440304</v>
       </c>
       <c r="W33">
-        <v>0.0639</v>
+        <v>0.1087738520408164</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.503938616603482</v>
+        <v>0.8932196739449325</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1895199108442191</v>
+        <v>0.1905299108442191</v>
       </c>
       <c r="C34">
-        <v>8.995304412419729</v>
+        <v>8.761035631421159</v>
       </c>
       <c r="D34">
-        <v>13.20750441241973</v>
+        <v>13.11533563142116</v>
       </c>
       <c r="E34">
-        <v>3.0372</v>
+        <v>3.1793</v>
       </c>
       <c r="F34">
-        <v>4.5472</v>
+        <v>4.6893</v>
       </c>
       <c r="G34">
         <v>0.335</v>
@@ -4069,37 +4069,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M34">
-        <v>0.6675289600000001</v>
+        <v>0.6883892400000001</v>
       </c>
       <c r="N34">
-        <v>-0.07127896000000011</v>
+        <v>-0.09213924000000018</v>
       </c>
       <c r="O34">
-        <v>-0.02067089840000003</v>
+        <v>-0.02672037960000005</v>
       </c>
       <c r="P34">
-        <v>-0.05060806160000008</v>
+        <v>-0.06541886040000013</v>
       </c>
       <c r="Q34">
-        <v>-0.04060806160000007</v>
+        <v>-0.05541886040000012</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2275180561634675</v>
+        <v>0.230230265956952</v>
       </c>
       <c r="T34">
-        <v>1.111365010374175</v>
+        <v>1.127952547842446</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2590337054440304</v>
+        <v>0.2511841992184537</v>
       </c>
       <c r="W34">
-        <v>0.1087738520408164</v>
+        <v>0.109926159554731</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8932196739449325</v>
+        <v>0.8661524110981162</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1905299108442191</v>
+        <v>0.1915399108442191</v>
       </c>
       <c r="C35">
-        <v>8.761035631421159</v>
+        <v>8.528044338082198</v>
       </c>
       <c r="D35">
-        <v>13.11533563142116</v>
+        <v>13.0244443380822</v>
       </c>
       <c r="E35">
-        <v>3.1793</v>
+        <v>3.321400000000001</v>
       </c>
       <c r="F35">
-        <v>4.6893</v>
+        <v>4.8314</v>
       </c>
       <c r="G35">
         <v>0.335</v>
@@ -4151,37 +4151,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M35">
-        <v>0.6883892400000001</v>
+        <v>0.7092495200000001</v>
       </c>
       <c r="N35">
-        <v>-0.09213924000000018</v>
+        <v>-0.1129995200000001</v>
       </c>
       <c r="O35">
-        <v>-0.02672037960000005</v>
+        <v>-0.03276986080000004</v>
       </c>
       <c r="P35">
-        <v>-0.06541886040000013</v>
+        <v>-0.08022965920000009</v>
       </c>
       <c r="Q35">
-        <v>-0.05541886040000012</v>
+        <v>-0.07022965920000009</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.230230265956952</v>
+        <v>0.2330246639259968</v>
       </c>
       <c r="T35">
-        <v>1.127952547842446</v>
+        <v>1.145042737961271</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2511841992184537</v>
+        <v>0.2437964286532051</v>
       </c>
       <c r="W35">
-        <v>0.109926159554731</v>
+        <v>0.1110106842737095</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8661524110981162</v>
+        <v>0.8406773401834658</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1915399108442191</v>
+        <v>0.1925499108442191</v>
       </c>
       <c r="C36">
-        <v>8.528044338082198</v>
+        <v>8.296304155639927</v>
       </c>
       <c r="D36">
-        <v>13.0244443380822</v>
+        <v>12.93480415563993</v>
       </c>
       <c r="E36">
-        <v>3.321400000000001</v>
+        <v>3.463500000000001</v>
       </c>
       <c r="F36">
-        <v>4.8314</v>
+        <v>4.9735</v>
       </c>
       <c r="G36">
         <v>0.335</v>
@@ -4233,37 +4233,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M36">
-        <v>0.7092495200000001</v>
+        <v>0.7301098000000001</v>
       </c>
       <c r="N36">
-        <v>-0.1129995200000001</v>
+        <v>-0.1338598000000002</v>
       </c>
       <c r="O36">
-        <v>-0.03276986080000004</v>
+        <v>-0.03881934200000006</v>
       </c>
       <c r="P36">
-        <v>-0.08022965920000009</v>
+        <v>-0.09504045800000013</v>
       </c>
       <c r="Q36">
-        <v>-0.07022965920000009</v>
+        <v>-0.08504045800000012</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2330246639259968</v>
+        <v>0.2359050433710121</v>
       </c>
       <c r="T36">
-        <v>1.145042737961271</v>
+        <v>1.162658780083752</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2437964286532051</v>
+        <v>0.2368308164059706</v>
       </c>
       <c r="W36">
-        <v>0.1110106842737095</v>
+        <v>0.1120332361516035</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8406773401834658</v>
+        <v>0.8166579876067953</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1925499108442191</v>
+        <v>0.2160033735673946</v>
       </c>
       <c r="C37">
-        <v>8.296304155639927</v>
+        <v>6.37183086457379</v>
       </c>
       <c r="D37">
-        <v>12.93480415563993</v>
+        <v>11.15243086457379</v>
       </c>
       <c r="E37">
-        <v>3.463500000000001</v>
+        <v>3.605600000000001</v>
       </c>
       <c r="F37">
-        <v>4.9735</v>
+        <v>5.115600000000001</v>
       </c>
       <c r="G37">
         <v>0.335</v>
@@ -4315,45 +4315,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M37">
-        <v>0.7301098000000001</v>
+        <v>1.02721248</v>
       </c>
       <c r="N37">
-        <v>-0.1338598000000002</v>
+        <v>-0.4309624800000003</v>
       </c>
       <c r="O37">
-        <v>-0.03881934200000006</v>
+        <v>-0.1249791192000001</v>
       </c>
       <c r="P37">
-        <v>-0.09504045800000013</v>
+        <v>-0.3059833608000002</v>
       </c>
       <c r="Q37">
-        <v>-0.08504045800000012</v>
+        <v>-0.2959833608000002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2359050433710121</v>
+        <v>0.2435683451786458</v>
       </c>
       <c r="T37">
-        <v>1.162658780083752</v>
+        <v>1.20952657997525</v>
       </c>
       <c r="U37">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.2368308164059706</v>
+        <v>0.1683317749410521</v>
       </c>
       <c r="W37">
-        <v>0.1120332361516035</v>
+        <v>0.1669989795918368</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8166579876067953</v>
+        <v>0.5804543963484554</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2160033735673946</v>
+        <v>0.2175533735673946</v>
       </c>
       <c r="C38">
-        <v>6.37183086457379</v>
+        <v>6.129084993805456</v>
       </c>
       <c r="D38">
-        <v>11.15243086457379</v>
+        <v>11.05178499380546</v>
       </c>
       <c r="E38">
-        <v>3.6056</v>
+        <v>3.7477</v>
       </c>
       <c r="F38">
-        <v>5.1156</v>
+        <v>5.2577</v>
       </c>
       <c r="G38">
         <v>0.335</v>
@@ -4397,37 +4397,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M38">
-        <v>1.02721248</v>
+        <v>1.05574616</v>
       </c>
       <c r="N38">
-        <v>-0.43096248</v>
+        <v>-0.45949616</v>
       </c>
       <c r="O38">
-        <v>-0.1249791192</v>
+        <v>-0.1332538864</v>
       </c>
       <c r="P38">
-        <v>-0.3059833608</v>
+        <v>-0.3262422736</v>
       </c>
       <c r="Q38">
-        <v>-0.2959833608</v>
+        <v>-0.3162422736</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2435683451786458</v>
+        <v>0.2467075252608466</v>
       </c>
       <c r="T38">
-        <v>1.20952657997525</v>
+        <v>1.228725414578032</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1683317749410521</v>
+        <v>0.1637822675102129</v>
       </c>
       <c r="W38">
-        <v>0.1669989795918367</v>
+        <v>0.1679125206839493</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5804543963484555</v>
+        <v>0.5647664396903891</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2175533735673946</v>
+        <v>0.2191033735673946</v>
       </c>
       <c r="C39">
-        <v>6.129084993805456</v>
+        <v>5.888139446902488</v>
       </c>
       <c r="D39">
-        <v>11.05178499380546</v>
+        <v>10.95293944690249</v>
       </c>
       <c r="E39">
-        <v>3.7477</v>
+        <v>3.8898</v>
       </c>
       <c r="F39">
-        <v>5.2577</v>
+        <v>5.3998</v>
       </c>
       <c r="G39">
         <v>0.335</v>
@@ -4479,37 +4479,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M39">
-        <v>1.05574616</v>
+        <v>1.08427984</v>
       </c>
       <c r="N39">
-        <v>-0.45949616</v>
+        <v>-0.48802984</v>
       </c>
       <c r="O39">
-        <v>-0.1332538864</v>
+        <v>-0.1415286536</v>
       </c>
       <c r="P39">
-        <v>-0.3262422736</v>
+        <v>-0.3465011864</v>
       </c>
       <c r="Q39">
-        <v>-0.3162422736</v>
+        <v>-0.3365011864</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2467075252608466</v>
+        <v>0.2499479692166667</v>
       </c>
       <c r="T39">
-        <v>1.228725414578032</v>
+        <v>1.248543566426064</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1637822675102129</v>
+        <v>0.1594722078388915</v>
       </c>
       <c r="W39">
-        <v>0.1679125206839493</v>
+        <v>0.1687779806659506</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5647664396903891</v>
+        <v>0.5499041649616947</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2191033735673946</v>
+        <v>0.2206533735673945</v>
       </c>
       <c r="C40">
-        <v>5.888139446902488</v>
+        <v>5.648946346573172</v>
       </c>
       <c r="D40">
-        <v>10.95293944690249</v>
+        <v>10.85584634657317</v>
       </c>
       <c r="E40">
-        <v>3.8898</v>
+        <v>4.0319</v>
       </c>
       <c r="F40">
-        <v>5.3998</v>
+        <v>5.5419</v>
       </c>
       <c r="G40">
         <v>0.335</v>
@@ -4561,37 +4561,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M40">
-        <v>1.08427984</v>
+        <v>1.11281352</v>
       </c>
       <c r="N40">
-        <v>-0.48802984</v>
+        <v>-0.5165635200000001</v>
       </c>
       <c r="O40">
-        <v>-0.1415286536</v>
+        <v>-0.1498034208</v>
       </c>
       <c r="P40">
-        <v>-0.3465011864</v>
+        <v>-0.3667600992000001</v>
       </c>
       <c r="Q40">
-        <v>-0.3365011864</v>
+        <v>-0.3567600992000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2499479692166667</v>
+        <v>0.253294657236612</v>
       </c>
       <c r="T40">
-        <v>1.248543566426064</v>
+        <v>1.269011493744524</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1594722078388915</v>
+        <v>0.1553831768686635</v>
       </c>
       <c r="W40">
-        <v>0.1687779806659506</v>
+        <v>0.1695990580847724</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5499041649616947</v>
+        <v>0.5358040581678051</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2206533735673945</v>
+        <v>0.2222033735673946</v>
       </c>
       <c r="C41">
-        <v>5.648946346573172</v>
+        <v>5.411459498255556</v>
       </c>
       <c r="D41">
-        <v>10.85584634657317</v>
+        <v>10.76045949825556</v>
       </c>
       <c r="E41">
-        <v>4.0319</v>
+        <v>4.174</v>
       </c>
       <c r="F41">
-        <v>5.5419</v>
+        <v>5.684</v>
       </c>
       <c r="G41">
         <v>0.335</v>
@@ -4643,37 +4643,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M41">
-        <v>1.11281352</v>
+        <v>1.1413472</v>
       </c>
       <c r="N41">
-        <v>-0.5165635200000001</v>
+        <v>-0.5450972000000001</v>
       </c>
       <c r="O41">
-        <v>-0.1498034208</v>
+        <v>-0.158078188</v>
       </c>
       <c r="P41">
-        <v>-0.3667600992000001</v>
+        <v>-0.3870190120000001</v>
       </c>
       <c r="Q41">
-        <v>-0.3567600992000001</v>
+        <v>-0.377019012</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.253294657236612</v>
+        <v>0.2567529015238889</v>
       </c>
       <c r="T41">
-        <v>1.269011493744524</v>
+        <v>1.290161685306933</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1553831768686635</v>
+        <v>0.1514985974469469</v>
       </c>
       <c r="W41">
-        <v>0.1695990580847724</v>
+        <v>0.1703790816326531</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5358040581678051</v>
+        <v>0.52240895671361</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2222033735673946</v>
+        <v>0.2237533735673946</v>
       </c>
       <c r="C42">
-        <v>5.411459498255556</v>
+        <v>5.175634316833358</v>
       </c>
       <c r="D42">
-        <v>10.76045949825556</v>
+        <v>10.66673431683336</v>
       </c>
       <c r="E42">
-        <v>4.174</v>
+        <v>4.3161</v>
       </c>
       <c r="F42">
-        <v>5.684</v>
+        <v>5.8261</v>
       </c>
       <c r="G42">
         <v>0.335</v>
@@ -4725,37 +4725,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M42">
-        <v>1.1413472</v>
+        <v>1.16988088</v>
       </c>
       <c r="N42">
-        <v>-0.5450972000000001</v>
+        <v>-0.5736308800000001</v>
       </c>
       <c r="O42">
-        <v>-0.158078188</v>
+        <v>-0.1663529552</v>
       </c>
       <c r="P42">
-        <v>-0.3870190120000001</v>
+        <v>-0.4072779248</v>
       </c>
       <c r="Q42">
-        <v>-0.377019012</v>
+        <v>-0.3972779248</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2567529015238889</v>
+        <v>0.2603283744310734</v>
       </c>
       <c r="T42">
-        <v>1.290161685306933</v>
+        <v>1.312028832515525</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1514985974469469</v>
+        <v>0.1478035097043384</v>
       </c>
       <c r="W42">
-        <v>0.1703790816326531</v>
+        <v>0.1711210552513689</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.52240895671361</v>
+        <v>0.5096672748425464</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2237533735673946</v>
+        <v>0.2412153070540025</v>
       </c>
       <c r="C43">
-        <v>5.175634316833358</v>
+        <v>4.08037559059095</v>
       </c>
       <c r="D43">
-        <v>10.66673431683336</v>
+        <v>9.713575590590949</v>
       </c>
       <c r="E43">
-        <v>4.3161</v>
+        <v>4.458200000000001</v>
       </c>
       <c r="F43">
-        <v>5.8261</v>
+        <v>5.9682</v>
       </c>
       <c r="G43">
         <v>0.335</v>
@@ -4807,45 +4807,45 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M43">
-        <v>1.16988088</v>
+        <v>1.40730156</v>
       </c>
       <c r="N43">
-        <v>-0.5736308800000001</v>
+        <v>-0.8110515600000001</v>
       </c>
       <c r="O43">
-        <v>-0.1663529552</v>
+        <v>-0.2352049524</v>
       </c>
       <c r="P43">
-        <v>-0.4072779248</v>
+        <v>-0.5758466076000001</v>
       </c>
       <c r="Q43">
-        <v>-0.3972779248</v>
+        <v>-0.5658466076000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2603283744310734</v>
+        <v>0.2661166800016228</v>
       </c>
       <c r="T43">
-        <v>1.312028832515525</v>
+        <v>1.347429388829399</v>
       </c>
       <c r="U43">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1478035097043384</v>
+        <v>0.1228681221670784</v>
       </c>
       <c r="W43">
-        <v>0.1711210552513689</v>
+        <v>0.2068276967930029</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.5096672748425464</v>
+        <v>0.4236831798864772</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2412153070540025</v>
+        <v>0.2431153070540025</v>
       </c>
       <c r="C44">
-        <v>4.08037559059095</v>
+        <v>3.844741065076051</v>
       </c>
       <c r="D44">
-        <v>9.713575590590949</v>
+        <v>9.62004106507605</v>
       </c>
       <c r="E44">
-        <v>4.4582</v>
+        <v>4.6003</v>
       </c>
       <c r="F44">
-        <v>5.9682</v>
+        <v>6.1103</v>
       </c>
       <c r="G44">
         <v>0.335</v>
@@ -4889,37 +4889,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M44">
-        <v>1.40730156</v>
+        <v>1.44080874</v>
       </c>
       <c r="N44">
-        <v>-0.8110515599999999</v>
+        <v>-0.8445587400000001</v>
       </c>
       <c r="O44">
-        <v>-0.2352049523999999</v>
+        <v>-0.2449220346</v>
       </c>
       <c r="P44">
-        <v>-0.5758466075999999</v>
+        <v>-0.5996367054</v>
       </c>
       <c r="Q44">
-        <v>-0.5658466075999999</v>
+        <v>-0.5896367054</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2661166800016228</v>
+        <v>0.2699818849139319</v>
       </c>
       <c r="T44">
-        <v>1.347429388829399</v>
+        <v>1.371068500914125</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1228681221670784</v>
+        <v>0.1200107239771463</v>
       </c>
       <c r="W44">
-        <v>0.2068276967930029</v>
+        <v>0.2075014712861889</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4236831798864772</v>
+        <v>0.4138300826798149</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2431153070540025</v>
+        <v>0.2450153070540025</v>
       </c>
       <c r="C45">
-        <v>3.844741065076051</v>
+        <v>3.6108906956193</v>
       </c>
       <c r="D45">
-        <v>9.62004106507605</v>
+        <v>9.528290695619299</v>
       </c>
       <c r="E45">
-        <v>4.6003</v>
+        <v>4.7424</v>
       </c>
       <c r="F45">
-        <v>6.1103</v>
+        <v>6.2524</v>
       </c>
       <c r="G45">
         <v>0.335</v>
@@ -4971,37 +4971,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M45">
-        <v>1.44080874</v>
+        <v>1.47431592</v>
       </c>
       <c r="N45">
-        <v>-0.8445587400000001</v>
+        <v>-0.8780659200000001</v>
       </c>
       <c r="O45">
-        <v>-0.2449220346</v>
+        <v>-0.2546391168</v>
       </c>
       <c r="P45">
-        <v>-0.5996367054</v>
+        <v>-0.6234268032000001</v>
       </c>
       <c r="Q45">
-        <v>-0.5896367054</v>
+        <v>-0.6134268032000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2699818849139319</v>
+        <v>0.2739851328588236</v>
       </c>
       <c r="T45">
-        <v>1.371068500914125</v>
+        <v>1.395551867001878</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1200107239771463</v>
+        <v>0.1172832075231203</v>
       </c>
       <c r="W45">
-        <v>0.2075014712861889</v>
+        <v>0.2081446196660482</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4138300826798149</v>
+        <v>0.4044248535280009</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2450153070540025</v>
+        <v>0.2469153070540025</v>
       </c>
       <c r="C46">
-        <v>3.6108906956193</v>
+        <v>3.378773915758704</v>
       </c>
       <c r="D46">
-        <v>9.528290695619299</v>
+        <v>9.438273915758703</v>
       </c>
       <c r="E46">
-        <v>4.7424</v>
+        <v>4.8845</v>
       </c>
       <c r="F46">
-        <v>6.2524</v>
+        <v>6.3945</v>
       </c>
       <c r="G46">
         <v>0.335</v>
@@ -5053,37 +5053,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M46">
-        <v>1.47431592</v>
+        <v>1.5078231</v>
       </c>
       <c r="N46">
-        <v>-0.8780659200000001</v>
+        <v>-0.9115731</v>
       </c>
       <c r="O46">
-        <v>-0.2546391168</v>
+        <v>-0.264356199</v>
       </c>
       <c r="P46">
-        <v>-0.6234268032000001</v>
+        <v>-0.647216901</v>
       </c>
       <c r="Q46">
-        <v>-0.6134268032000001</v>
+        <v>-0.6372169009999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2739851328588236</v>
+        <v>0.2781339534562567</v>
       </c>
       <c r="T46">
-        <v>1.395551867001878</v>
+        <v>1.420925537311002</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1172832075231203</v>
+        <v>0.1146769140226065</v>
       </c>
       <c r="W46">
-        <v>0.2081446196660482</v>
+        <v>0.2087591836734694</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4044248535280009</v>
+        <v>0.395437634560712</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2469153070540025</v>
+        <v>0.2488153070540025</v>
       </c>
       <c r="C47">
-        <v>3.378773915758704</v>
+        <v>3.148342052018146</v>
       </c>
       <c r="D47">
-        <v>9.438273915758703</v>
+        <v>9.349942052018145</v>
       </c>
       <c r="E47">
-        <v>4.8845</v>
+        <v>5.0266</v>
       </c>
       <c r="F47">
-        <v>6.3945</v>
+        <v>6.5366</v>
       </c>
       <c r="G47">
         <v>0.335</v>
@@ -5135,37 +5135,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M47">
-        <v>1.5078231</v>
+        <v>1.54133028</v>
       </c>
       <c r="N47">
-        <v>-0.9115731</v>
+        <v>-0.9450802800000002</v>
       </c>
       <c r="O47">
-        <v>-0.264356199</v>
+        <v>-0.2740732812</v>
       </c>
       <c r="P47">
-        <v>-0.647216901</v>
+        <v>-0.6710069988000003</v>
       </c>
       <c r="Q47">
-        <v>-0.6372169009999999</v>
+        <v>-0.6610069988000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2781339534562567</v>
+        <v>0.2824364340758171</v>
       </c>
       <c r="T47">
-        <v>1.420925537311002</v>
+        <v>1.447238973187132</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1146769140226065</v>
+        <v>0.1121839376308107</v>
       </c>
       <c r="W47">
-        <v>0.2087591836734694</v>
+        <v>0.2093470275066548</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.395437634560712</v>
+        <v>0.3868411642441748</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2488153070540025</v>
+        <v>0.2507153070540025</v>
       </c>
       <c r="C48">
-        <v>3.148342052018146</v>
+        <v>2.919548236147413</v>
       </c>
       <c r="D48">
-        <v>9.349942052018145</v>
+        <v>9.263248236147412</v>
       </c>
       <c r="E48">
-        <v>5.0266</v>
+        <v>5.1687</v>
       </c>
       <c r="F48">
-        <v>6.5366</v>
+        <v>6.6787</v>
       </c>
       <c r="G48">
         <v>0.335</v>
@@ -5217,37 +5217,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M48">
-        <v>1.54133028</v>
+        <v>1.57483746</v>
       </c>
       <c r="N48">
-        <v>-0.9450802800000002</v>
+        <v>-0.9785874600000002</v>
       </c>
       <c r="O48">
-        <v>-0.2740732812</v>
+        <v>-0.2837903634</v>
       </c>
       <c r="P48">
-        <v>-0.6710069988000003</v>
+        <v>-0.6947970966000001</v>
       </c>
       <c r="Q48">
-        <v>-0.6610069988000002</v>
+        <v>-0.6847970966000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2824364340758171</v>
+        <v>0.2869012724546061</v>
       </c>
       <c r="T48">
-        <v>1.447238973187132</v>
+        <v>1.474545368907644</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1121839376308107</v>
+        <v>0.1097970453407934</v>
       </c>
       <c r="W48">
-        <v>0.2093470275066548</v>
+        <v>0.2099098567086409</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3868411642441748</v>
+        <v>0.3786105011751498</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2507153070540025</v>
+        <v>0.2526153070540025</v>
       </c>
       <c r="C49">
-        <v>2.919548236147413</v>
+        <v>2.692347322199664</v>
       </c>
       <c r="D49">
-        <v>9.263248236147412</v>
+        <v>9.178147322199663</v>
       </c>
       <c r="E49">
-        <v>5.1687</v>
+        <v>5.3108</v>
       </c>
       <c r="F49">
-        <v>6.6787</v>
+        <v>6.8208</v>
       </c>
       <c r="G49">
         <v>0.335</v>
@@ -5299,37 +5299,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M49">
-        <v>1.57483746</v>
+        <v>1.60834464</v>
       </c>
       <c r="N49">
-        <v>-0.9785874600000002</v>
+        <v>-1.01209464</v>
       </c>
       <c r="O49">
-        <v>-0.2837903634</v>
+        <v>-0.2935074456</v>
       </c>
       <c r="P49">
-        <v>-0.6947970966000001</v>
+        <v>-0.7185871944000002</v>
       </c>
       <c r="Q49">
-        <v>-0.6847970966000001</v>
+        <v>-0.7085871944000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2869012724546061</v>
+        <v>0.2915378353864254</v>
       </c>
       <c r="T49">
-        <v>1.474545368907644</v>
+        <v>1.502902010617406</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1097970453407934</v>
+        <v>0.1075096068961936</v>
       </c>
       <c r="W49">
-        <v>0.2099098567086409</v>
+        <v>0.2104492346938776</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3786105011751498</v>
+        <v>0.3707227824006675</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2526153070540024</v>
+        <v>0.2545153070540025</v>
       </c>
       <c r="C50">
-        <v>2.692347322199667</v>
+        <v>2.46669580813813</v>
       </c>
       <c r="D50">
-        <v>9.178147322199665</v>
+        <v>9.094595808138129</v>
       </c>
       <c r="E50">
-        <v>5.3108</v>
+        <v>5.4529</v>
       </c>
       <c r="F50">
-        <v>6.820799999999999</v>
+        <v>6.962899999999999</v>
       </c>
       <c r="G50">
         <v>0.335</v>
@@ -5381,37 +5381,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M50">
-        <v>1.60834464</v>
+        <v>1.64185182</v>
       </c>
       <c r="N50">
-        <v>-1.01209464</v>
+        <v>-1.04560182</v>
       </c>
       <c r="O50">
-        <v>-0.2935074456</v>
+        <v>-0.3032245278</v>
       </c>
       <c r="P50">
-        <v>-0.7185871944</v>
+        <v>-0.7423772921999999</v>
       </c>
       <c r="Q50">
-        <v>-0.7085871944</v>
+        <v>-0.7323772921999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2915378353864254</v>
+        <v>0.296356224315571</v>
       </c>
       <c r="T50">
-        <v>1.502902010617406</v>
+        <v>1.532370677492258</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1075096068961936</v>
+        <v>0.1053155332860672</v>
       </c>
       <c r="W50">
-        <v>0.2104492346938776</v>
+        <v>0.2109665972511454</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3707227824006676</v>
+        <v>0.3631570113312662</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2545153070540025</v>
+        <v>0.2564153070540025</v>
       </c>
       <c r="C51">
-        <v>2.46669580813813</v>
+        <v>2.242551761686031</v>
       </c>
       <c r="D51">
-        <v>9.094595808138129</v>
+        <v>9.01255176168603</v>
       </c>
       <c r="E51">
-        <v>5.4529</v>
+        <v>5.595</v>
       </c>
       <c r="F51">
-        <v>6.962899999999999</v>
+        <v>7.105</v>
       </c>
       <c r="G51">
         <v>0.335</v>
@@ -5463,37 +5463,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M51">
-        <v>1.64185182</v>
+        <v>1.675359</v>
       </c>
       <c r="N51">
-        <v>-1.04560182</v>
+        <v>-1.079109</v>
       </c>
       <c r="O51">
-        <v>-0.3032245278</v>
+        <v>-0.31294161</v>
       </c>
       <c r="P51">
-        <v>-0.7423772921999999</v>
+        <v>-0.7661673900000001</v>
       </c>
       <c r="Q51">
-        <v>-0.7323772921999999</v>
+        <v>-0.7561673900000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.296356224315571</v>
+        <v>0.3013673488018824</v>
       </c>
       <c r="T51">
-        <v>1.532370677492258</v>
+        <v>1.563018091042103</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1053155332860672</v>
+        <v>0.1032092226203458</v>
       </c>
       <c r="W51">
-        <v>0.2109665972511454</v>
+        <v>0.2114632653061225</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3631570113312662</v>
+        <v>0.3558938711046408</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2564153070540025</v>
+        <v>0.2583153070540025</v>
       </c>
       <c r="C52">
-        <v>2.242551761686031</v>
+        <v>2.019874750154093</v>
       </c>
       <c r="D52">
-        <v>9.01255176168603</v>
+        <v>8.931974750154092</v>
       </c>
       <c r="E52">
-        <v>5.595</v>
+        <v>5.7371</v>
       </c>
       <c r="F52">
-        <v>7.105</v>
+        <v>7.2471</v>
       </c>
       <c r="G52">
         <v>0.335</v>
@@ -5545,37 +5545,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M52">
-        <v>1.675359</v>
+        <v>1.70886618</v>
       </c>
       <c r="N52">
-        <v>-1.079109</v>
+        <v>-1.11261618</v>
       </c>
       <c r="O52">
-        <v>-0.31294161</v>
+        <v>-0.3226586922</v>
       </c>
       <c r="P52">
-        <v>-0.7661673900000001</v>
+        <v>-0.7899574878000001</v>
       </c>
       <c r="Q52">
-        <v>-0.7561673900000001</v>
+        <v>-0.7799574878000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3013673488018824</v>
+        <v>0.3065830089815127</v>
       </c>
       <c r="T52">
-        <v>1.563018091042103</v>
+        <v>1.594916419430717</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1032092226203458</v>
+        <v>0.1011855123728881</v>
       </c>
       <c r="W52">
-        <v>0.2114632653061225</v>
+        <v>0.211940456182473</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3558938711046408</v>
+        <v>0.3489155599065106</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2583153070540025</v>
+        <v>0.2602153070540025</v>
       </c>
       <c r="C53">
-        <v>2.019874750154093</v>
+        <v>1.798625773999052</v>
       </c>
       <c r="D53">
-        <v>8.931974750154092</v>
+        <v>8.852825773999051</v>
       </c>
       <c r="E53">
-        <v>5.7371</v>
+        <v>5.8792</v>
       </c>
       <c r="F53">
-        <v>7.2471</v>
+        <v>7.3892</v>
       </c>
       <c r="G53">
         <v>0.335</v>
@@ -5627,37 +5627,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M53">
-        <v>1.70886618</v>
+        <v>1.74237336</v>
       </c>
       <c r="N53">
-        <v>-1.11261618</v>
+        <v>-1.14612336</v>
       </c>
       <c r="O53">
-        <v>-0.3226586922</v>
+        <v>-0.3323757744</v>
       </c>
       <c r="P53">
-        <v>-0.7899574878000001</v>
+        <v>-0.8137475856</v>
       </c>
       <c r="Q53">
-        <v>-0.7799574878000001</v>
+        <v>-0.8037475856</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3065830089815127</v>
+        <v>0.3120159883352943</v>
       </c>
       <c r="T53">
-        <v>1.594916419430717</v>
+        <v>1.628143844835524</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1011855123728881</v>
+        <v>0.09923963713494791</v>
       </c>
       <c r="W53">
-        <v>0.211940456182473</v>
+        <v>0.2123992935635793</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3489155599065106</v>
+        <v>0.3422056452929239</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2602153070540025</v>
+        <v>0.2621153070540024</v>
       </c>
       <c r="C54">
-        <v>1.798625773999052</v>
+        <v>1.578767203883631</v>
       </c>
       <c r="D54">
-        <v>8.852825773999051</v>
+        <v>8.77506720388363</v>
       </c>
       <c r="E54">
-        <v>5.8792</v>
+        <v>6.0213</v>
       </c>
       <c r="F54">
-        <v>7.3892</v>
+        <v>7.5313</v>
       </c>
       <c r="G54">
         <v>0.335</v>
@@ -5709,37 +5709,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M54">
-        <v>1.74237336</v>
+        <v>1.77588054</v>
       </c>
       <c r="N54">
-        <v>-1.14612336</v>
+        <v>-1.17963054</v>
       </c>
       <c r="O54">
-        <v>-0.3323757744</v>
+        <v>-0.3420928566</v>
       </c>
       <c r="P54">
-        <v>-0.8137475856</v>
+        <v>-0.8375376834</v>
       </c>
       <c r="Q54">
-        <v>-0.8037475856</v>
+        <v>-0.8275376834</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3120159883352943</v>
+        <v>0.3176801582998749</v>
       </c>
       <c r="T54">
-        <v>1.628143844835524</v>
+        <v>1.66278520323628</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.09923963713494791</v>
+        <v>0.09736719115126966</v>
       </c>
       <c r="W54">
-        <v>0.2123992935635793</v>
+        <v>0.2128408163265306</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3422056452929239</v>
+        <v>0.3357489350043782</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2621153070540024</v>
+        <v>0.2640153070540024</v>
       </c>
       <c r="C55">
-        <v>1.578767203883631</v>
+        <v>1.36026272102463</v>
       </c>
       <c r="D55">
-        <v>8.77506720388363</v>
+        <v>8.698662721024629</v>
       </c>
       <c r="E55">
-        <v>6.0213</v>
+        <v>6.1634</v>
       </c>
       <c r="F55">
-        <v>7.5313</v>
+        <v>7.6734</v>
       </c>
       <c r="G55">
         <v>0.335</v>
@@ -5791,37 +5791,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M55">
-        <v>1.77588054</v>
+        <v>1.80938772</v>
       </c>
       <c r="N55">
-        <v>-1.17963054</v>
+        <v>-1.21313772</v>
       </c>
       <c r="O55">
-        <v>-0.3420928566</v>
+        <v>-0.3518099388000001</v>
       </c>
       <c r="P55">
-        <v>-0.8375376834</v>
+        <v>-0.8613277812000002</v>
       </c>
       <c r="Q55">
-        <v>-0.8275376834</v>
+        <v>-0.8513277812000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3176801582998749</v>
+        <v>0.3235905965237853</v>
       </c>
       <c r="T55">
-        <v>1.66278520323628</v>
+        <v>1.69893270765446</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.09736719115126966</v>
+        <v>0.09556409501883872</v>
       </c>
       <c r="W55">
-        <v>0.2128408163265306</v>
+        <v>0.2132659863945578</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3357489350043782</v>
+        <v>0.3295313621339266</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2640153070540024</v>
+        <v>0.2659153070540025</v>
       </c>
       <c r="C56">
-        <v>1.36026272102463</v>
+        <v>1.143077260630491</v>
       </c>
       <c r="D56">
-        <v>8.698662721024629</v>
+        <v>8.623577260630491</v>
       </c>
       <c r="E56">
-        <v>6.1634</v>
+        <v>6.3055</v>
       </c>
       <c r="F56">
-        <v>7.6734</v>
+        <v>7.8155</v>
       </c>
       <c r="G56">
         <v>0.335</v>
@@ -5873,37 +5873,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M56">
-        <v>1.80938772</v>
+        <v>1.8428949</v>
       </c>
       <c r="N56">
-        <v>-1.21313772</v>
+        <v>-1.2466449</v>
       </c>
       <c r="O56">
-        <v>-0.3518099388000001</v>
+        <v>-0.361527021</v>
       </c>
       <c r="P56">
-        <v>-0.8613277812000002</v>
+        <v>-0.8851178790000002</v>
       </c>
       <c r="Q56">
-        <v>-0.8513277812000002</v>
+        <v>-0.8751178790000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3235905965237853</v>
+        <v>0.3297637208909805</v>
       </c>
       <c r="T56">
-        <v>1.69893270765446</v>
+        <v>1.736686767824559</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.09556409501883872</v>
+        <v>0.09382656601849619</v>
       </c>
       <c r="W56">
-        <v>0.2132659863945578</v>
+        <v>0.2136756957328386</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3295313621339266</v>
+        <v>0.3235398828224008</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2659153070540025</v>
+        <v>0.2678153070540025</v>
       </c>
       <c r="C57">
-        <v>1.143077260630491</v>
+        <v>0.9271769582431757</v>
       </c>
       <c r="D57">
-        <v>8.623577260630491</v>
+        <v>8.549776958243175</v>
       </c>
       <c r="E57">
-        <v>6.3055</v>
+        <v>6.4476</v>
       </c>
       <c r="F57">
-        <v>7.8155</v>
+        <v>7.9576</v>
       </c>
       <c r="G57">
         <v>0.335</v>
@@ -5955,37 +5955,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M57">
-        <v>1.8428949</v>
+        <v>1.87640208</v>
       </c>
       <c r="N57">
-        <v>-1.2466449</v>
+        <v>-1.28015208</v>
       </c>
       <c r="O57">
-        <v>-0.361527021</v>
+        <v>-0.3712441032</v>
       </c>
       <c r="P57">
-        <v>-0.8851178790000002</v>
+        <v>-0.9089079768000001</v>
       </c>
       <c r="Q57">
-        <v>-0.8751178790000002</v>
+        <v>-0.8989079768000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3297637208909805</v>
+        <v>0.336217441820321</v>
       </c>
       <c r="T57">
-        <v>1.736686767824559</v>
+        <v>1.776156921638753</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09382656601849619</v>
+        <v>0.09215109162530878</v>
       </c>
       <c r="W57">
-        <v>0.2136756957328386</v>
+        <v>0.2140707725947522</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3235398828224008</v>
+        <v>0.3177623849148579</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2678153070540025</v>
+        <v>0.2697153070540025</v>
       </c>
       <c r="C58">
-        <v>0.9271769582431757</v>
+        <v>0.7125290988119097</v>
       </c>
       <c r="D58">
-        <v>8.549776958243175</v>
+        <v>8.477229098811909</v>
       </c>
       <c r="E58">
-        <v>6.4476</v>
+        <v>6.589700000000001</v>
       </c>
       <c r="F58">
-        <v>7.9576</v>
+        <v>8.0997</v>
       </c>
       <c r="G58">
         <v>0.335</v>
@@ -6037,37 +6037,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M58">
-        <v>1.87640208</v>
+        <v>1.90990926</v>
       </c>
       <c r="N58">
-        <v>-1.28015208</v>
+        <v>-1.31365926</v>
       </c>
       <c r="O58">
-        <v>-0.3712441032</v>
+        <v>-0.3809611854</v>
       </c>
       <c r="P58">
-        <v>-0.9089079768000001</v>
+        <v>-0.9326980746000001</v>
       </c>
       <c r="Q58">
-        <v>-0.8989079768000001</v>
+        <v>-0.9226980746000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.336217441820321</v>
+        <v>0.3429713358161425</v>
       </c>
       <c r="T58">
-        <v>1.776156921638753</v>
+        <v>1.817462896560585</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09215109162530878</v>
+        <v>0.09053440580732092</v>
       </c>
       <c r="W58">
-        <v>0.2140707725947522</v>
+        <v>0.2144519871106337</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3177623849148579</v>
+        <v>0.312187606232141</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2697153070540025</v>
+        <v>0.2716153070540025</v>
       </c>
       <c r="C59">
-        <v>0.7125290988119097</v>
+        <v>0.4991020683378835</v>
       </c>
       <c r="D59">
-        <v>8.477229098811909</v>
+        <v>8.405902068337884</v>
       </c>
       <c r="E59">
-        <v>6.589700000000001</v>
+        <v>6.731800000000002</v>
       </c>
       <c r="F59">
-        <v>8.0997</v>
+        <v>8.241800000000001</v>
       </c>
       <c r="G59">
         <v>0.335</v>
@@ -6119,37 +6119,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M59">
-        <v>1.90990926</v>
+        <v>1.94341644</v>
       </c>
       <c r="N59">
-        <v>-1.31365926</v>
+        <v>-1.347166440000001</v>
       </c>
       <c r="O59">
-        <v>-0.3809611854</v>
+        <v>-0.3906782676000001</v>
       </c>
       <c r="P59">
-        <v>-0.9326980746000001</v>
+        <v>-0.9564881724000004</v>
       </c>
       <c r="Q59">
-        <v>-0.9226980746000001</v>
+        <v>-0.9464881724000004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3429713358161425</v>
+        <v>0.3500468438117649</v>
       </c>
       <c r="T59">
-        <v>1.817462896560585</v>
+        <v>1.86073582266917</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09053440580732092</v>
+        <v>0.08897346777616019</v>
       </c>
       <c r="W59">
-        <v>0.2144519871106337</v>
+        <v>0.2148200562983814</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.312187606232141</v>
+        <v>0.3068050612971041</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2716153070540024</v>
+        <v>0.2735153070540025</v>
       </c>
       <c r="C60">
-        <v>0.4991020683378871</v>
+        <v>0.2868653079397188</v>
       </c>
       <c r="D60">
-        <v>8.405902068337886</v>
+        <v>8.335765307939717</v>
       </c>
       <c r="E60">
-        <v>6.7318</v>
+        <v>6.873899999999999</v>
       </c>
       <c r="F60">
-        <v>8.2418</v>
+        <v>8.383899999999999</v>
       </c>
       <c r="G60">
         <v>0.335</v>
@@ -6201,37 +6201,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M60">
-        <v>1.94341644</v>
+        <v>1.97692362</v>
       </c>
       <c r="N60">
-        <v>-1.34716644</v>
+        <v>-1.38067362</v>
       </c>
       <c r="O60">
-        <v>-0.3906782676</v>
+        <v>-0.4003953497999999</v>
       </c>
       <c r="P60">
-        <v>-0.9564881724000001</v>
+        <v>-0.9802782701999999</v>
       </c>
       <c r="Q60">
-        <v>-0.9464881724</v>
+        <v>-0.9702782701999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3500468438117648</v>
+        <v>0.357467498538881</v>
       </c>
       <c r="T60">
-        <v>1.86073582266917</v>
+        <v>1.906119623222077</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08897346777616021</v>
+        <v>0.08746544289859817</v>
       </c>
       <c r="W60">
-        <v>0.2148200562983814</v>
+        <v>0.2151756485645106</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3068050612971042</v>
+        <v>0.3016049755124075</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2735153070540025</v>
+        <v>0.2754153070540024</v>
       </c>
       <c r="C61">
-        <v>0.2868653079397188</v>
+        <v>0.07578927019951287</v>
       </c>
       <c r="D61">
-        <v>8.335765307939717</v>
+        <v>8.266789270199512</v>
       </c>
       <c r="E61">
-        <v>6.873899999999999</v>
+        <v>7.016</v>
       </c>
       <c r="F61">
-        <v>8.383899999999999</v>
+        <v>8.526</v>
       </c>
       <c r="G61">
         <v>0.335</v>
@@ -6283,37 +6283,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M61">
-        <v>1.97692362</v>
+        <v>2.0104308</v>
       </c>
       <c r="N61">
-        <v>-1.38067362</v>
+        <v>-1.4141808</v>
       </c>
       <c r="O61">
-        <v>-0.4003953497999999</v>
+        <v>-0.410112432</v>
       </c>
       <c r="P61">
-        <v>-0.9802782701999999</v>
+        <v>-1.004068368</v>
       </c>
       <c r="Q61">
-        <v>-0.9702782701999999</v>
+        <v>-0.994068368</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.357467498538881</v>
+        <v>0.365259186002353</v>
       </c>
       <c r="T61">
-        <v>1.906119623222077</v>
+        <v>1.953772613802628</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08746544289859817</v>
+        <v>0.08600768551695485</v>
       </c>
       <c r="W61">
-        <v>0.2151756485645106</v>
+        <v>0.2155193877551021</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3016049755124075</v>
+        <v>0.2965782259205341</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2754153070540024</v>
+        <v>0.2773153070540024</v>
       </c>
       <c r="C62">
-        <v>0.07578927019951287</v>
+        <v>-0.1341546223415317</v>
       </c>
       <c r="D62">
-        <v>8.266789270199512</v>
+        <v>8.198945377658466</v>
       </c>
       <c r="E62">
-        <v>7.016</v>
+        <v>7.158099999999999</v>
       </c>
       <c r="F62">
-        <v>8.526</v>
+        <v>8.668099999999999</v>
       </c>
       <c r="G62">
         <v>0.335</v>
@@ -6365,37 +6365,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M62">
-        <v>2.0104308</v>
+        <v>2.04393798</v>
       </c>
       <c r="N62">
-        <v>-1.4141808</v>
+        <v>-1.44768798</v>
       </c>
       <c r="O62">
-        <v>-0.410112432</v>
+        <v>-0.4198295142</v>
       </c>
       <c r="P62">
-        <v>-1.004068368</v>
+        <v>-1.0278584658</v>
       </c>
       <c r="Q62">
-        <v>-0.994068368</v>
+        <v>-1.0178584658</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.365259186002353</v>
+        <v>0.3734504471819006</v>
       </c>
       <c r="T62">
-        <v>1.953772613802628</v>
+        <v>2.003869347489875</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08600768551695485</v>
+        <v>0.08459772345929986</v>
       </c>
       <c r="W62">
-        <v>0.2155193877551021</v>
+        <v>0.2158518568082971</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2965782259205341</v>
+        <v>0.2917162877906893</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2773153070540024</v>
+        <v>0.2792153070540024</v>
       </c>
       <c r="C63">
-        <v>-0.1341546223415317</v>
+        <v>-0.3429940166604624</v>
       </c>
       <c r="D63">
-        <v>8.198945377658466</v>
+        <v>8.132205983339537</v>
       </c>
       <c r="E63">
-        <v>7.158099999999999</v>
+        <v>7.3002</v>
       </c>
       <c r="F63">
-        <v>8.668099999999999</v>
+        <v>8.8102</v>
       </c>
       <c r="G63">
         <v>0.335</v>
@@ -6447,37 +6447,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M63">
-        <v>2.04393798</v>
+        <v>2.07744516</v>
       </c>
       <c r="N63">
-        <v>-1.44768798</v>
+        <v>-1.48119516</v>
       </c>
       <c r="O63">
-        <v>-0.4198295142</v>
+        <v>-0.4295465964</v>
       </c>
       <c r="P63">
-        <v>-1.0278584658</v>
+        <v>-1.0516485636</v>
       </c>
       <c r="Q63">
-        <v>-1.0178584658</v>
+        <v>-1.0416485636</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3734504471819006</v>
+        <v>0.3820728273708979</v>
       </c>
       <c r="T63">
-        <v>2.003869347489875</v>
+        <v>2.056602751371188</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08459772345929986</v>
+        <v>0.083233244048666</v>
       </c>
       <c r="W63">
-        <v>0.2158518568082971</v>
+        <v>0.2161736010533246</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2917162877906893</v>
+        <v>0.2870111863747103</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2792153070540024</v>
+        <v>0.2811153070540025</v>
       </c>
       <c r="C64">
-        <v>-0.3429940166604624</v>
+        <v>-0.5507556668173681</v>
       </c>
       <c r="D64">
-        <v>8.132205983339537</v>
+        <v>8.06654433318263</v>
       </c>
       <c r="E64">
-        <v>7.3002</v>
+        <v>7.442299999999999</v>
       </c>
       <c r="F64">
-        <v>8.8102</v>
+        <v>8.952299999999999</v>
       </c>
       <c r="G64">
         <v>0.335</v>
@@ -6529,37 +6529,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M64">
-        <v>2.07744516</v>
+        <v>2.11095234</v>
       </c>
       <c r="N64">
-        <v>-1.48119516</v>
+        <v>-1.51470234</v>
       </c>
       <c r="O64">
-        <v>-0.4295465964</v>
+        <v>-0.4392636785999999</v>
       </c>
       <c r="P64">
-        <v>-1.0516485636</v>
+        <v>-1.0754386614</v>
       </c>
       <c r="Q64">
-        <v>-1.0416485636</v>
+        <v>-1.0654386614</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3820728273708979</v>
+        <v>0.391161282164706</v>
       </c>
       <c r="T64">
-        <v>2.056602751371188</v>
+        <v>2.112186609516355</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.083233244048666</v>
+        <v>0.08191208144471893</v>
       </c>
       <c r="W64">
-        <v>0.2161736010533246</v>
+        <v>0.2164851311953353</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2870111863747103</v>
+        <v>0.2824554532576514</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2811153070540025</v>
+        <v>0.2830153070540025</v>
       </c>
       <c r="C65">
-        <v>-0.5507556668173681</v>
+        <v>-0.7574654697149459</v>
       </c>
       <c r="D65">
-        <v>8.06654433318263</v>
+        <v>8.001934530285054</v>
       </c>
       <c r="E65">
-        <v>7.442299999999999</v>
+        <v>7.5844</v>
       </c>
       <c r="F65">
-        <v>8.952299999999999</v>
+        <v>9.0944</v>
       </c>
       <c r="G65">
         <v>0.335</v>
@@ -6611,37 +6611,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M65">
-        <v>2.11095234</v>
+        <v>2.14445952</v>
       </c>
       <c r="N65">
-        <v>-1.51470234</v>
+        <v>-1.54820952</v>
       </c>
       <c r="O65">
-        <v>-0.4392636785999999</v>
+        <v>-0.4489807608</v>
       </c>
       <c r="P65">
-        <v>-1.0754386614</v>
+        <v>-1.0992287592</v>
       </c>
       <c r="Q65">
-        <v>-1.0654386614</v>
+        <v>-1.0892287592</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.391161282164706</v>
+        <v>0.4007546511137257</v>
       </c>
       <c r="T65">
-        <v>2.112186609516355</v>
+        <v>2.170858459780698</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08191208144471893</v>
+        <v>0.08063220517214517</v>
       </c>
       <c r="W65">
-        <v>0.2164851311953353</v>
+        <v>0.2167869260204082</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2824554532576514</v>
+        <v>0.2780420868005006</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2830153070540025</v>
+        <v>0.2849153070540024</v>
       </c>
       <c r="C66">
-        <v>-0.7574654697149459</v>
+        <v>-0.9631484991531565</v>
       </c>
       <c r="D66">
-        <v>8.001934530285054</v>
+        <v>7.938351500846843</v>
       </c>
       <c r="E66">
-        <v>7.5844</v>
+        <v>7.7265</v>
       </c>
       <c r="F66">
-        <v>9.0944</v>
+        <v>9.236499999999999</v>
       </c>
       <c r="G66">
         <v>0.335</v>
@@ -6693,37 +6693,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M66">
-        <v>2.14445952</v>
+        <v>2.1779667</v>
       </c>
       <c r="N66">
-        <v>-1.54820952</v>
+        <v>-1.5817167</v>
       </c>
       <c r="O66">
-        <v>-0.4489807608</v>
+        <v>-0.4586978429999999</v>
       </c>
       <c r="P66">
-        <v>-1.0992287592</v>
+        <v>-1.123018857</v>
       </c>
       <c r="Q66">
-        <v>-1.0892287592</v>
+        <v>-1.113018857</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4007546511137257</v>
+        <v>0.4108962125741177</v>
       </c>
       <c r="T66">
-        <v>2.170858459780698</v>
+        <v>2.232882987203004</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08063220517214517</v>
+        <v>0.07939170970795834</v>
       </c>
       <c r="W66">
-        <v>0.2167869260204082</v>
+        <v>0.2170794348508634</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2780420868005006</v>
+        <v>0.2737645162343392</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2849153070540024</v>
+        <v>0.2868153070540025</v>
       </c>
       <c r="C67">
-        <v>-0.9631484991531565</v>
+        <v>-1.167829038273148</v>
       </c>
       <c r="D67">
-        <v>7.938351500846843</v>
+        <v>7.875770961726852</v>
       </c>
       <c r="E67">
-        <v>7.7265</v>
+        <v>7.868600000000001</v>
       </c>
       <c r="F67">
-        <v>9.236499999999999</v>
+        <v>9.3786</v>
       </c>
       <c r="G67">
         <v>0.335</v>
@@ -6775,37 +6775,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M67">
-        <v>2.1779667</v>
+        <v>2.21147388</v>
       </c>
       <c r="N67">
-        <v>-1.5817167</v>
+        <v>-1.61522388</v>
       </c>
       <c r="O67">
-        <v>-0.4586978429999999</v>
+        <v>-0.4684149252000001</v>
       </c>
       <c r="P67">
-        <v>-1.123018857</v>
+        <v>-1.1468089548</v>
       </c>
       <c r="Q67">
-        <v>-1.113018857</v>
+        <v>-1.1368089548</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4108962125741177</v>
+        <v>0.4216343364733565</v>
       </c>
       <c r="T67">
-        <v>2.232882987203004</v>
+        <v>2.298556016238386</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07939170970795834</v>
+        <v>0.0781888050154135</v>
       </c>
       <c r="W67">
-        <v>0.2170794348508634</v>
+        <v>0.2173630797773655</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2737645162343392</v>
+        <v>0.2696165690186673</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2868153070540025</v>
+        <v>0.2887153070540025</v>
       </c>
       <c r="C68">
-        <v>-1.167829038273148</v>
+        <v>-1.371530610478533</v>
       </c>
       <c r="D68">
-        <v>7.875770961726852</v>
+        <v>7.814169389521465</v>
       </c>
       <c r="E68">
-        <v>7.868600000000001</v>
+        <v>8.0107</v>
       </c>
       <c r="F68">
-        <v>9.3786</v>
+        <v>9.5207</v>
       </c>
       <c r="G68">
         <v>0.335</v>
@@ -6857,37 +6857,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M68">
-        <v>2.21147388</v>
+        <v>2.24498106</v>
       </c>
       <c r="N68">
-        <v>-1.61522388</v>
+        <v>-1.64873106</v>
       </c>
       <c r="O68">
-        <v>-0.4684149252000001</v>
+        <v>-0.4781320074000001</v>
       </c>
       <c r="P68">
-        <v>-1.1468089548</v>
+        <v>-1.1705990526</v>
       </c>
       <c r="Q68">
-        <v>-1.1368089548</v>
+        <v>-1.1605990526</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4216343364733565</v>
+        <v>0.433023255760428</v>
       </c>
       <c r="T68">
-        <v>2.298556016238386</v>
+        <v>2.368209228851671</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0781888050154135</v>
+        <v>0.07702180792563122</v>
       </c>
       <c r="W68">
-        <v>0.2173630797773655</v>
+        <v>0.2176382576911362</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2696165690186673</v>
+        <v>0.2655924411228663</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2887153070540025</v>
+        <v>0.2906153070540025</v>
       </c>
       <c r="C69">
-        <v>-1.371530610478533</v>
+        <v>-1.574276008916859</v>
       </c>
       <c r="D69">
-        <v>7.814169389521465</v>
+        <v>7.75352399108314</v>
       </c>
       <c r="E69">
-        <v>8.0107</v>
+        <v>8.152800000000001</v>
       </c>
       <c r="F69">
-        <v>9.5207</v>
+        <v>9.662800000000001</v>
       </c>
       <c r="G69">
         <v>0.335</v>
@@ -6939,37 +6939,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M69">
-        <v>2.24498106</v>
+        <v>2.27848824</v>
       </c>
       <c r="N69">
-        <v>-1.64873106</v>
+        <v>-1.68223824</v>
       </c>
       <c r="O69">
-        <v>-0.4781320074000001</v>
+        <v>-0.4878490896</v>
       </c>
       <c r="P69">
-        <v>-1.1705990526</v>
+        <v>-1.1943891504</v>
       </c>
       <c r="Q69">
-        <v>-1.1605990526</v>
+        <v>-1.1843891504</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.433023255760428</v>
+        <v>0.4451239825029414</v>
       </c>
       <c r="T69">
-        <v>2.368209228851671</v>
+        <v>2.442215767253286</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07702180792563122</v>
+        <v>0.07588913427966605</v>
       </c>
       <c r="W69">
-        <v>0.2176382576911362</v>
+        <v>0.2179053421368548</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2655924411228663</v>
+        <v>0.261686669929883</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2906153070540025</v>
+        <v>0.2925153070540025</v>
       </c>
       <c r="C70">
-        <v>-1.574276008916859</v>
+        <v>-1.776087324598757</v>
       </c>
       <c r="D70">
-        <v>7.75352399108314</v>
+        <v>7.693812675401242</v>
       </c>
       <c r="E70">
-        <v>8.152800000000001</v>
+        <v>8.2949</v>
       </c>
       <c r="F70">
-        <v>9.662800000000001</v>
+        <v>9.8049</v>
       </c>
       <c r="G70">
         <v>0.335</v>
@@ -7021,37 +7021,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M70">
-        <v>2.27848824</v>
+        <v>2.31199542</v>
       </c>
       <c r="N70">
-        <v>-1.68223824</v>
+        <v>-1.71574542</v>
       </c>
       <c r="O70">
-        <v>-0.4878490896</v>
+        <v>-0.4975661718</v>
       </c>
       <c r="P70">
-        <v>-1.1943891504</v>
+        <v>-1.2181792482</v>
       </c>
       <c r="Q70">
-        <v>-1.1843891504</v>
+        <v>-1.2081792482</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4451239825029414</v>
+        <v>0.4580054012933589</v>
       </c>
       <c r="T70">
-        <v>2.442215767253286</v>
+        <v>2.52099692103565</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07588913427966605</v>
+        <v>0.07478929175387379</v>
       </c>
       <c r="W70">
-        <v>0.2179053421368548</v>
+        <v>0.2181646850044366</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.261686669929883</v>
+        <v>0.2578941094961166</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2925153070540025</v>
+        <v>0.2944153070540024</v>
       </c>
       <c r="C71">
-        <v>-1.776087324598757</v>
+        <v>-1.976985973227769</v>
       </c>
       <c r="D71">
-        <v>7.693812675401242</v>
+        <v>7.635014026772232</v>
       </c>
       <c r="E71">
-        <v>8.2949</v>
+        <v>8.437000000000001</v>
       </c>
       <c r="F71">
-        <v>9.8049</v>
+        <v>9.947000000000001</v>
       </c>
       <c r="G71">
         <v>0.335</v>
@@ -7103,37 +7103,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M71">
-        <v>2.31199542</v>
+        <v>2.3455026</v>
       </c>
       <c r="N71">
-        <v>-1.71574542</v>
+        <v>-1.7492526</v>
       </c>
       <c r="O71">
-        <v>-0.4975661718</v>
+        <v>-0.507283254</v>
       </c>
       <c r="P71">
-        <v>-1.2181792482</v>
+        <v>-1.241969346</v>
       </c>
       <c r="Q71">
-        <v>-1.2081792482</v>
+        <v>-1.231969346</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4580054012933589</v>
+        <v>0.4717455813364708</v>
       </c>
       <c r="T71">
-        <v>2.52099692103565</v>
+        <v>2.605030151736838</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07478929175387379</v>
+        <v>0.07372087330024703</v>
       </c>
       <c r="W71">
-        <v>0.2181646850044366</v>
+        <v>0.2184166180758018</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2578941094961166</v>
+        <v>0.2542099079318862</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2944153070540024</v>
+        <v>0.2963153070540025</v>
       </c>
       <c r="C72">
-        <v>-1.976985973227769</v>
+        <v>-2.176992720809227</v>
       </c>
       <c r="D72">
-        <v>7.635014026772232</v>
+        <v>7.577107279190773</v>
       </c>
       <c r="E72">
-        <v>8.437000000000001</v>
+        <v>8.5791</v>
       </c>
       <c r="F72">
-        <v>9.947000000000001</v>
+        <v>10.0891</v>
       </c>
       <c r="G72">
         <v>0.335</v>
@@ -7185,37 +7185,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M72">
-        <v>2.3455026</v>
+        <v>2.37900978</v>
       </c>
       <c r="N72">
-        <v>-1.7492526</v>
+        <v>-1.78275978</v>
       </c>
       <c r="O72">
-        <v>-0.507283254</v>
+        <v>-0.5170003362</v>
       </c>
       <c r="P72">
-        <v>-1.241969346</v>
+        <v>-1.2657594438</v>
       </c>
       <c r="Q72">
-        <v>-1.231969346</v>
+        <v>-1.2557594438</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4717455813364708</v>
+        <v>0.4864333600032457</v>
       </c>
       <c r="T72">
-        <v>2.605030151736838</v>
+        <v>2.694858777658799</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07372087330024703</v>
+        <v>0.07268255114108861</v>
       </c>
       <c r="W72">
-        <v>0.2184166180758018</v>
+        <v>0.2186614544409313</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2542099079318862</v>
+        <v>0.250629486693409</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2963153070540024</v>
+        <v>0.2982153070540025</v>
       </c>
       <c r="C73">
-        <v>-2.176992720809225</v>
+        <v>-2.376127708102537</v>
       </c>
       <c r="D73">
-        <v>7.577107279190773</v>
+        <v>7.520072291897463</v>
       </c>
       <c r="E73">
-        <v>8.579099999999999</v>
+        <v>8.7212</v>
       </c>
       <c r="F73">
-        <v>10.0891</v>
+        <v>10.2312</v>
       </c>
       <c r="G73">
         <v>0.335</v>
@@ -7267,37 +7267,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M73">
-        <v>2.37900978</v>
+        <v>2.41251696</v>
       </c>
       <c r="N73">
-        <v>-1.78275978</v>
+        <v>-1.81626696</v>
       </c>
       <c r="O73">
-        <v>-0.5170003361999999</v>
+        <v>-0.5267174184</v>
       </c>
       <c r="P73">
-        <v>-1.2657594438</v>
+        <v>-1.2895495416</v>
       </c>
       <c r="Q73">
-        <v>-1.2557594438</v>
+        <v>-1.2795495416</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4864333600032456</v>
+        <v>0.5021702657176472</v>
       </c>
       <c r="T73">
-        <v>2.694858777658798</v>
+        <v>2.791103734003755</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07268255114108862</v>
+        <v>0.07167307126412904</v>
       </c>
       <c r="W73">
-        <v>0.2186614544409313</v>
+        <v>0.2188994897959184</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2506294866934091</v>
+        <v>0.247148521600445</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2982153070540025</v>
+        <v>0.3001153070540025</v>
       </c>
       <c r="C74">
-        <v>-2.376127708102537</v>
+        <v>-2.574410473977386</v>
       </c>
       <c r="D74">
-        <v>7.520072291897463</v>
+        <v>7.463889526022613</v>
       </c>
       <c r="E74">
-        <v>8.7212</v>
+        <v>8.863299999999999</v>
       </c>
       <c r="F74">
-        <v>10.2312</v>
+        <v>10.3733</v>
       </c>
       <c r="G74">
         <v>0.335</v>
@@ -7349,37 +7349,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M74">
-        <v>2.41251696</v>
+        <v>2.44602414</v>
       </c>
       <c r="N74">
-        <v>-1.81626696</v>
+        <v>-1.84977414</v>
       </c>
       <c r="O74">
-        <v>-0.5267174184</v>
+        <v>-0.5364345005999999</v>
       </c>
       <c r="P74">
-        <v>-1.2895495416</v>
+        <v>-1.3133396394</v>
       </c>
       <c r="Q74">
-        <v>-1.2795495416</v>
+        <v>-1.3033396394</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.5021702657176472</v>
+        <v>0.5190728681516341</v>
       </c>
       <c r="T74">
-        <v>2.791103734003755</v>
+        <v>2.894477946374264</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07167307126412904</v>
+        <v>0.07069124837009991</v>
       </c>
       <c r="W74">
-        <v>0.2188994897959184</v>
+        <v>0.2191310036343305</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.247148521600445</v>
+        <v>0.2437629254141376</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3001153070540025</v>
+        <v>0.3020153070540025</v>
       </c>
       <c r="C75">
-        <v>-2.574410473977386</v>
+        <v>-2.771859977730704</v>
       </c>
       <c r="D75">
-        <v>7.463889526022613</v>
+        <v>7.408540022269295</v>
       </c>
       <c r="E75">
-        <v>8.863299999999999</v>
+        <v>9.0054</v>
       </c>
       <c r="F75">
-        <v>10.3733</v>
+        <v>10.5154</v>
       </c>
       <c r="G75">
         <v>0.335</v>
@@ -7431,37 +7431,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M75">
-        <v>2.44602414</v>
+        <v>2.47953132</v>
       </c>
       <c r="N75">
-        <v>-1.84977414</v>
+        <v>-1.88328132</v>
       </c>
       <c r="O75">
-        <v>-0.5364345005999999</v>
+        <v>-0.5461515828</v>
       </c>
       <c r="P75">
-        <v>-1.3133396394</v>
+        <v>-1.3371297372</v>
       </c>
       <c r="Q75">
-        <v>-1.3033396394</v>
+        <v>-1.3271297372</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5190728681516341</v>
+        <v>0.5372756707728508</v>
       </c>
       <c r="T75">
-        <v>2.894477946374264</v>
+        <v>3.005804021234812</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07069124837009991</v>
+        <v>0.06973596122996339</v>
       </c>
       <c r="W75">
-        <v>0.2191310036343305</v>
+        <v>0.2193562603419746</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2437629254141376</v>
+        <v>0.24046883182746</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3020153070540025</v>
+        <v>0.3039153070540024</v>
       </c>
       <c r="C76">
-        <v>-2.771859977730704</v>
+        <v>-2.968494620417998</v>
       </c>
       <c r="D76">
-        <v>7.408540022269295</v>
+        <v>7.354005379582</v>
       </c>
       <c r="E76">
-        <v>9.0054</v>
+        <v>9.147499999999999</v>
       </c>
       <c r="F76">
-        <v>10.5154</v>
+        <v>10.6575</v>
       </c>
       <c r="G76">
         <v>0.335</v>
@@ -7513,37 +7513,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M76">
-        <v>2.47953132</v>
+        <v>2.5130385</v>
       </c>
       <c r="N76">
-        <v>-1.88328132</v>
+        <v>-1.9167885</v>
       </c>
       <c r="O76">
-        <v>-0.5461515828</v>
+        <v>-0.555868665</v>
       </c>
       <c r="P76">
-        <v>-1.3371297372</v>
+        <v>-1.360919835</v>
       </c>
       <c r="Q76">
-        <v>-1.3271297372</v>
+        <v>-1.350919835</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5372756707728508</v>
+        <v>0.5569346976037648</v>
       </c>
       <c r="T76">
-        <v>3.005804021234812</v>
+        <v>3.126036182084206</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06973596122996339</v>
+        <v>0.06880614841356389</v>
       </c>
       <c r="W76">
-        <v>0.2193562603419746</v>
+        <v>0.2195755102040816</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.24046883182746</v>
+        <v>0.2372625807364273</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3039153070540024</v>
+        <v>0.3058153070540024</v>
       </c>
       <c r="C77">
-        <v>-2.968494620417998</v>
+        <v>-3.164332265249441</v>
       </c>
       <c r="D77">
-        <v>7.354005379582</v>
+        <v>7.300267734750559</v>
       </c>
       <c r="E77">
-        <v>9.147499999999999</v>
+        <v>9.2896</v>
       </c>
       <c r="F77">
-        <v>10.6575</v>
+        <v>10.7996</v>
       </c>
       <c r="G77">
         <v>0.335</v>
@@ -7595,37 +7595,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M77">
-        <v>2.5130385</v>
+        <v>2.54654568</v>
       </c>
       <c r="N77">
-        <v>-1.9167885</v>
+        <v>-1.95029568</v>
       </c>
       <c r="O77">
-        <v>-0.555868665</v>
+        <v>-0.5655857472</v>
       </c>
       <c r="P77">
-        <v>-1.360919835</v>
+        <v>-1.3847099328</v>
       </c>
       <c r="Q77">
-        <v>-1.350919835</v>
+        <v>-1.3747099328</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5569346976037648</v>
+        <v>0.5782319766705885</v>
       </c>
       <c r="T77">
-        <v>3.126036182084206</v>
+        <v>3.256287689671048</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06880614841356389</v>
+        <v>0.06790080435549067</v>
       </c>
       <c r="W77">
-        <v>0.2195755102040816</v>
+        <v>0.2197889903329753</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2372625807364273</v>
+        <v>0.2341407046741059</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3058153070540024</v>
+        <v>0.3077153070540025</v>
       </c>
       <c r="C78">
-        <v>-3.164332265249441</v>
+        <v>-3.359390257098179</v>
       </c>
       <c r="D78">
-        <v>7.300267734750559</v>
+        <v>7.247309742901821</v>
       </c>
       <c r="E78">
-        <v>9.2896</v>
+        <v>9.431699999999999</v>
       </c>
       <c r="F78">
-        <v>10.7996</v>
+        <v>10.9417</v>
       </c>
       <c r="G78">
         <v>0.335</v>
@@ -7677,37 +7677,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M78">
-        <v>2.54654568</v>
+        <v>2.58005286</v>
       </c>
       <c r="N78">
-        <v>-1.95029568</v>
+        <v>-1.98380286</v>
       </c>
       <c r="O78">
-        <v>-0.5655857472</v>
+        <v>-0.5753028294</v>
       </c>
       <c r="P78">
-        <v>-1.3847099328</v>
+        <v>-1.4085000306</v>
       </c>
       <c r="Q78">
-        <v>-1.3747099328</v>
+        <v>-1.3985000306</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5782319766705885</v>
+        <v>0.6013811930475705</v>
       </c>
       <c r="T78">
-        <v>3.256287689671048</v>
+        <v>3.39786541530892</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06790080435549067</v>
+        <v>0.06701897572749729</v>
       </c>
       <c r="W78">
-        <v>0.2197889903329753</v>
+        <v>0.2199969255234561</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2341407046741059</v>
+        <v>0.2310999163017148</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3077153070540025</v>
+        <v>0.3096153070540024</v>
       </c>
       <c r="C79">
-        <v>-3.359390257098179</v>
+        <v>-3.553685441165702</v>
       </c>
       <c r="D79">
-        <v>7.247309742901821</v>
+        <v>7.195114558834298</v>
       </c>
       <c r="E79">
-        <v>9.431699999999999</v>
+        <v>9.5738</v>
       </c>
       <c r="F79">
-        <v>10.9417</v>
+        <v>11.0838</v>
       </c>
       <c r="G79">
         <v>0.335</v>
@@ -7759,37 +7759,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M79">
-        <v>2.58005286</v>
+        <v>2.61356004</v>
       </c>
       <c r="N79">
-        <v>-1.98380286</v>
+        <v>-2.01731004</v>
       </c>
       <c r="O79">
-        <v>-0.5753028294</v>
+        <v>-0.5850199116000001</v>
       </c>
       <c r="P79">
-        <v>-1.4085000306</v>
+        <v>-1.4322901284</v>
       </c>
       <c r="Q79">
-        <v>-1.3985000306</v>
+        <v>-1.4222901284</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6013811930475705</v>
+        <v>0.6266348836406419</v>
       </c>
       <c r="T79">
-        <v>3.39786541530892</v>
+        <v>3.552313843277506</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06701897572749729</v>
+        <v>0.06615975808996527</v>
       </c>
       <c r="W79">
-        <v>0.2199969255234561</v>
+        <v>0.2201995290423862</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2310999163017148</v>
+        <v>0.2281370968619493</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3096153070540024</v>
+        <v>0.3115153070540024</v>
       </c>
       <c r="C80">
-        <v>-3.553685441165702</v>
+        <v>-3.747234180846349</v>
       </c>
       <c r="D80">
-        <v>7.195114558834298</v>
+        <v>7.14366581915365</v>
       </c>
       <c r="E80">
-        <v>9.5738</v>
+        <v>9.7159</v>
       </c>
       <c r="F80">
-        <v>11.0838</v>
+        <v>11.2259</v>
       </c>
       <c r="G80">
         <v>0.335</v>
@@ -7841,37 +7841,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M80">
-        <v>2.61356004</v>
+        <v>2.64706722</v>
       </c>
       <c r="N80">
-        <v>-2.01731004</v>
+        <v>-2.05081722</v>
       </c>
       <c r="O80">
-        <v>-0.5850199116000001</v>
+        <v>-0.5947369937999999</v>
       </c>
       <c r="P80">
-        <v>-1.4322901284</v>
+        <v>-1.4560802262</v>
       </c>
       <c r="Q80">
-        <v>-1.4222901284</v>
+        <v>-1.4460802262</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6266348836406419</v>
+        <v>0.6542936876235297</v>
       </c>
       <c r="T80">
-        <v>3.552313843277506</v>
+        <v>3.72147164533834</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06615975808996527</v>
+        <v>0.06532229279768724</v>
       </c>
       <c r="W80">
-        <v>0.2201995290423862</v>
+        <v>0.2203970033583054</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2281370968619493</v>
+        <v>0.2252492855092664</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3115153070540024</v>
+        <v>0.3134153070540024</v>
       </c>
       <c r="C81">
-        <v>-3.747234180846349</v>
+        <v>-3.940052374830872</v>
       </c>
       <c r="D81">
-        <v>7.14366581915365</v>
+        <v>7.092947625169129</v>
       </c>
       <c r="E81">
-        <v>9.7159</v>
+        <v>9.858000000000001</v>
       </c>
       <c r="F81">
-        <v>11.2259</v>
+        <v>11.368</v>
       </c>
       <c r="G81">
         <v>0.335</v>
@@ -7923,37 +7923,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M81">
-        <v>2.64706722</v>
+        <v>2.6805744</v>
       </c>
       <c r="N81">
-        <v>-2.05081722</v>
+        <v>-2.0843244</v>
       </c>
       <c r="O81">
-        <v>-0.5947369937999999</v>
+        <v>-0.604454076</v>
       </c>
       <c r="P81">
-        <v>-1.4560802262</v>
+        <v>-1.479870324</v>
       </c>
       <c r="Q81">
-        <v>-1.4460802262</v>
+        <v>-1.469870324</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.6542936876235297</v>
+        <v>0.6847183720047062</v>
       </c>
       <c r="T81">
-        <v>3.72147164533834</v>
+        <v>3.907545227605258</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06532229279768724</v>
+        <v>0.06450576413771614</v>
       </c>
       <c r="W81">
-        <v>0.2203970033583054</v>
+        <v>0.2205895408163265</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2252492855092664</v>
+        <v>0.2224336694404005</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3134153070540024</v>
+        <v>0.3153153070540025</v>
       </c>
       <c r="C82">
-        <v>-3.940052374830872</v>
+        <v>-4.132155473486493</v>
       </c>
       <c r="D82">
-        <v>7.092947625169129</v>
+        <v>7.042944526513507</v>
       </c>
       <c r="E82">
-        <v>9.858000000000001</v>
+        <v>10.0001</v>
       </c>
       <c r="F82">
-        <v>11.368</v>
+        <v>11.5101</v>
       </c>
       <c r="G82">
         <v>0.335</v>
@@ -8005,37 +8005,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M82">
-        <v>2.6805744</v>
+        <v>2.71408158</v>
       </c>
       <c r="N82">
-        <v>-2.0843244</v>
+        <v>-2.11783158</v>
       </c>
       <c r="O82">
-        <v>-0.604454076</v>
+        <v>-0.6141711582</v>
       </c>
       <c r="P82">
-        <v>-1.479870324</v>
+        <v>-1.5036604218</v>
       </c>
       <c r="Q82">
-        <v>-1.469870324</v>
+        <v>-1.4936604218</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6847183720047062</v>
+        <v>0.718345654741796</v>
       </c>
       <c r="T82">
-        <v>3.907545227605258</v>
+        <v>4.113205502742376</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06450576413771614</v>
+        <v>0.06370939667922582</v>
       </c>
       <c r="W82">
-        <v>0.2205895408163265</v>
+        <v>0.2207773242630386</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2224336694404005</v>
+        <v>0.2196875747559511</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3153153070540025</v>
+        <v>0.3172153070540025</v>
       </c>
       <c r="C83">
-        <v>-4.132155473486493</v>
+        <v>-4.323558494549021</v>
       </c>
       <c r="D83">
-        <v>7.042944526513507</v>
+        <v>6.99364150545098</v>
       </c>
       <c r="E83">
-        <v>10.0001</v>
+        <v>10.1422</v>
       </c>
       <c r="F83">
-        <v>11.5101</v>
+        <v>11.6522</v>
       </c>
       <c r="G83">
         <v>0.335</v>
@@ -8087,37 +8087,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M83">
-        <v>2.71408158</v>
+        <v>2.74758876</v>
       </c>
       <c r="N83">
-        <v>-2.11783158</v>
+        <v>-2.15133876</v>
       </c>
       <c r="O83">
-        <v>-0.6141711582</v>
+        <v>-0.6238882404</v>
       </c>
       <c r="P83">
-        <v>-1.5036604218</v>
+        <v>-1.5274505196</v>
       </c>
       <c r="Q83">
-        <v>-1.4936604218</v>
+        <v>-1.5174505196</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.718345654741796</v>
+        <v>0.7557093022274514</v>
       </c>
       <c r="T83">
-        <v>4.113205502742376</v>
+        <v>4.341716919561398</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06370939667922582</v>
+        <v>0.06293245281728405</v>
       </c>
       <c r="W83">
-        <v>0.2207773242630386</v>
+        <v>0.2209605276256844</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2196875747559511</v>
+        <v>0.2170084579906346</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3172153070540025</v>
+        <v>0.3191153070540024</v>
       </c>
       <c r="C84">
-        <v>-4.323558494549021</v>
+        <v>-4.514276038160403</v>
       </c>
       <c r="D84">
-        <v>6.99364150545098</v>
+        <v>6.945023961839596</v>
       </c>
       <c r="E84">
-        <v>10.1422</v>
+        <v>10.2843</v>
       </c>
       <c r="F84">
-        <v>11.6522</v>
+        <v>11.7943</v>
       </c>
       <c r="G84">
         <v>0.335</v>
@@ -8169,37 +8169,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M84">
-        <v>2.74758876</v>
+        <v>2.78109594</v>
       </c>
       <c r="N84">
-        <v>-2.15133876</v>
+        <v>-2.18484594</v>
       </c>
       <c r="O84">
-        <v>-0.6238882404</v>
+        <v>-0.6336053226</v>
       </c>
       <c r="P84">
-        <v>-1.5274505196</v>
+        <v>-1.5512406174</v>
       </c>
       <c r="Q84">
-        <v>-1.5174505196</v>
+        <v>-1.5412406174</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7557093022274514</v>
+        <v>0.7974686729467132</v>
       </c>
       <c r="T84">
-        <v>4.341716919561398</v>
+        <v>4.597112032476774</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06293245281728405</v>
+        <v>0.06217423049418423</v>
       </c>
       <c r="W84">
-        <v>0.2209605276256844</v>
+        <v>0.2211393164494714</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2170084579906346</v>
+        <v>0.2143938982558077</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3191153070540024</v>
+        <v>0.3210153070540024</v>
       </c>
       <c r="C85">
-        <v>-4.514276038160403</v>
+        <v>-4.70432230128343</v>
       </c>
       <c r="D85">
-        <v>6.945023961839596</v>
+        <v>6.897077698716571</v>
       </c>
       <c r="E85">
-        <v>10.2843</v>
+        <v>10.4264</v>
       </c>
       <c r="F85">
-        <v>11.7943</v>
+        <v>11.9364</v>
       </c>
       <c r="G85">
         <v>0.335</v>
@@ -8251,37 +8251,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M85">
-        <v>2.78109594</v>
+        <v>2.81460312</v>
       </c>
       <c r="N85">
-        <v>-2.18484594</v>
+        <v>-2.21835312</v>
       </c>
       <c r="O85">
-        <v>-0.6336053226</v>
+        <v>-0.6433224048</v>
       </c>
       <c r="P85">
-        <v>-1.5512406174</v>
+        <v>-1.5750307152</v>
       </c>
       <c r="Q85">
-        <v>-1.5412406174</v>
+        <v>-1.5650307152</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7974686729467132</v>
+        <v>0.8444479650058829</v>
       </c>
       <c r="T85">
-        <v>4.597112032476774</v>
+        <v>4.884431534506573</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06217423049418423</v>
+        <v>0.06143406108353918</v>
       </c>
       <c r="W85">
-        <v>0.2211393164494714</v>
+        <v>0.2213138483965015</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2143938982558077</v>
+        <v>0.2118415899432385</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3210153070540024</v>
+        <v>0.3229153070540024</v>
       </c>
       <c r="C86">
-        <v>-4.704322301283426</v>
+        <v>-4.893711091523396</v>
       </c>
       <c r="D86">
-        <v>6.897077698716573</v>
+        <v>6.849788908476603</v>
       </c>
       <c r="E86">
-        <v>10.4264</v>
+        <v>10.5685</v>
       </c>
       <c r="F86">
-        <v>11.9364</v>
+        <v>12.0785</v>
       </c>
       <c r="G86">
         <v>0.335</v>
@@ -8333,37 +8333,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M86">
-        <v>2.81460312</v>
+        <v>2.8481103</v>
       </c>
       <c r="N86">
-        <v>-2.21835312</v>
+        <v>-2.2518603</v>
       </c>
       <c r="O86">
-        <v>-0.6433224047999999</v>
+        <v>-0.6530394869999999</v>
       </c>
       <c r="P86">
-        <v>-1.5750307152</v>
+        <v>-1.598820813</v>
       </c>
       <c r="Q86">
-        <v>-1.5650307152</v>
+        <v>-1.588820813</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8444479650058824</v>
+        <v>0.8976911626729412</v>
       </c>
       <c r="T86">
-        <v>4.88443153450657</v>
+        <v>5.210060303473675</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06143406108353919</v>
+        <v>0.06071130742373285</v>
       </c>
       <c r="W86">
-        <v>0.2213138483965015</v>
+        <v>0.2214842737094838</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2118415899432387</v>
+        <v>0.2093493359439064</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3229153070540024</v>
+        <v>0.3248153070540025</v>
       </c>
       <c r="C87">
-        <v>-4.893711091523396</v>
+        <v>-5.082455840385102</v>
       </c>
       <c r="D87">
-        <v>6.849788908476603</v>
+        <v>6.803144159614897</v>
       </c>
       <c r="E87">
-        <v>10.5685</v>
+        <v>10.7106</v>
       </c>
       <c r="F87">
-        <v>12.0785</v>
+        <v>12.2206</v>
       </c>
       <c r="G87">
         <v>0.335</v>
@@ -8415,37 +8415,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M87">
-        <v>2.8481103</v>
+        <v>2.88161748</v>
       </c>
       <c r="N87">
-        <v>-2.2518603</v>
+        <v>-2.28536748</v>
       </c>
       <c r="O87">
-        <v>-0.6530394869999999</v>
+        <v>-0.6627565692</v>
       </c>
       <c r="P87">
-        <v>-1.598820813</v>
+        <v>-1.6226109108</v>
       </c>
       <c r="Q87">
-        <v>-1.588820813</v>
+        <v>-1.6126109108</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8976911626729412</v>
+        <v>0.9585405314352944</v>
       </c>
       <c r="T87">
-        <v>5.210060303473675</v>
+        <v>5.58220746800751</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06071130742373285</v>
+        <v>0.06000536198857316</v>
       </c>
       <c r="W87">
-        <v>0.2214842737094838</v>
+        <v>0.2216507356430945</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2093493359439064</v>
+        <v>0.2069150413399075</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3248153070540025</v>
+        <v>0.3267153070540024</v>
       </c>
       <c r="C88">
-        <v>-5.082455840385102</v>
+        <v>-5.270569615991795</v>
       </c>
       <c r="D88">
-        <v>6.803144159614897</v>
+        <v>6.757130384008204</v>
       </c>
       <c r="E88">
-        <v>10.7106</v>
+        <v>10.8527</v>
       </c>
       <c r="F88">
-        <v>12.2206</v>
+        <v>12.3627</v>
       </c>
       <c r="G88">
         <v>0.335</v>
@@ -8497,37 +8497,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M88">
-        <v>2.88161748</v>
+        <v>2.91512466</v>
       </c>
       <c r="N88">
-        <v>-2.28536748</v>
+        <v>-2.31887466</v>
       </c>
       <c r="O88">
-        <v>-0.6627565692</v>
+        <v>-0.6724736513999998</v>
       </c>
       <c r="P88">
-        <v>-1.6226109108</v>
+        <v>-1.6464010086</v>
       </c>
       <c r="Q88">
-        <v>-1.6126109108</v>
+        <v>-1.6364010086</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.9585405314352944</v>
+        <v>1.028751341545701</v>
       </c>
       <c r="T88">
-        <v>5.58220746800751</v>
+        <v>6.011608042469625</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06000536198857316</v>
+        <v>0.05931564518410681</v>
       </c>
       <c r="W88">
-        <v>0.2216507356430945</v>
+        <v>0.2218133708655876</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2069150413399075</v>
+        <v>0.2045367075314029</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3267153070540024</v>
+        <v>0.3286153070540024</v>
       </c>
       <c r="C89">
-        <v>-5.270569615991795</v>
+        <v>-5.45806513529148</v>
       </c>
       <c r="D89">
-        <v>6.757130384008204</v>
+        <v>6.71173486470852</v>
       </c>
       <c r="E89">
-        <v>10.8527</v>
+        <v>10.9948</v>
       </c>
       <c r="F89">
-        <v>12.3627</v>
+        <v>12.5048</v>
       </c>
       <c r="G89">
         <v>0.335</v>
@@ -8579,37 +8579,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M89">
-        <v>2.91512466</v>
+        <v>2.94863184</v>
       </c>
       <c r="N89">
-        <v>-2.31887466</v>
+        <v>-2.35238184</v>
       </c>
       <c r="O89">
-        <v>-0.6724736513999998</v>
+        <v>-0.6821907335999999</v>
       </c>
       <c r="P89">
-        <v>-1.6464010086</v>
+        <v>-1.6701911064</v>
       </c>
       <c r="Q89">
-        <v>-1.6364010086</v>
+        <v>-1.6601911064</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.028751341545701</v>
+        <v>1.110663953341177</v>
       </c>
       <c r="T89">
-        <v>6.011608042469625</v>
+        <v>6.512575379342096</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05931564518410681</v>
+        <v>0.05864160376156013</v>
       </c>
       <c r="W89">
-        <v>0.2218133708655876</v>
+        <v>0.2219723098330241</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2045367075314029</v>
+        <v>0.2022124267640004</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3286153070540024</v>
+        <v>0.3305153070540024</v>
       </c>
       <c r="C90">
-        <v>-5.45806513529148</v>
+        <v>-5.644954775774446</v>
       </c>
       <c r="D90">
-        <v>6.71173486470852</v>
+        <v>6.666945224225553</v>
       </c>
       <c r="E90">
-        <v>10.9948</v>
+        <v>11.1369</v>
       </c>
       <c r="F90">
-        <v>12.5048</v>
+        <v>12.6469</v>
       </c>
       <c r="G90">
         <v>0.335</v>
@@ -8661,37 +8661,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M90">
-        <v>2.94863184</v>
+        <v>2.98213902</v>
       </c>
       <c r="N90">
-        <v>-2.35238184</v>
+        <v>-2.38588902</v>
       </c>
       <c r="O90">
-        <v>-0.6821907335999999</v>
+        <v>-0.6919078157999999</v>
       </c>
       <c r="P90">
-        <v>-1.6701911064</v>
+        <v>-1.6939812042</v>
       </c>
       <c r="Q90">
-        <v>-1.6601911064</v>
+        <v>-1.6839812042</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.110663953341177</v>
+        <v>1.207469767281284</v>
       </c>
       <c r="T90">
-        <v>6.512575379342096</v>
+        <v>7.104627686555013</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05864160376156013</v>
+        <v>0.05798270933727294</v>
       </c>
       <c r="W90">
-        <v>0.2219723098330241</v>
+        <v>0.2221276771382711</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2022124267640004</v>
+        <v>0.1999403770250792</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3305153070540024</v>
+        <v>0.3324153070540025</v>
       </c>
       <c r="C91">
-        <v>-5.644954775774446</v>
+        <v>-5.831250586724773</v>
       </c>
       <c r="D91">
-        <v>6.666945224225553</v>
+        <v>6.622749413275227</v>
       </c>
       <c r="E91">
-        <v>11.1369</v>
+        <v>11.279</v>
       </c>
       <c r="F91">
-        <v>12.6469</v>
+        <v>12.789</v>
       </c>
       <c r="G91">
         <v>0.335</v>
@@ -8743,37 +8743,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M91">
-        <v>2.98213902</v>
+        <v>3.0156462</v>
       </c>
       <c r="N91">
-        <v>-2.38588902</v>
+        <v>-2.4193962</v>
       </c>
       <c r="O91">
-        <v>-0.6919078157999999</v>
+        <v>-0.7016248979999999</v>
       </c>
       <c r="P91">
-        <v>-1.6939812042</v>
+        <v>-1.717771302</v>
       </c>
       <c r="Q91">
-        <v>-1.6839812042</v>
+        <v>-1.707771302</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.207469767281284</v>
+        <v>1.323636744009412</v>
       </c>
       <c r="T91">
-        <v>7.104627686555013</v>
+        <v>7.815090455210514</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05798270933727294</v>
+        <v>0.05733845701130324</v>
       </c>
       <c r="W91">
-        <v>0.2221276771382711</v>
+        <v>0.2222795918367347</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1999403770250792</v>
+        <v>0.197718817280356</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3324153070540025</v>
+        <v>0.3343153070540025</v>
       </c>
       <c r="C92">
-        <v>-5.831250586724773</v>
+        <v>-6.016964300027228</v>
       </c>
       <c r="D92">
-        <v>6.622749413275227</v>
+        <v>6.579135699972771</v>
       </c>
       <c r="E92">
-        <v>11.279</v>
+        <v>11.4211</v>
       </c>
       <c r="F92">
-        <v>12.789</v>
+        <v>12.9311</v>
       </c>
       <c r="G92">
         <v>0.335</v>
@@ -8825,37 +8825,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M92">
-        <v>3.0156462</v>
+        <v>3.04915338</v>
       </c>
       <c r="N92">
-        <v>-2.4193962</v>
+        <v>-2.45290338</v>
       </c>
       <c r="O92">
-        <v>-0.7016248979999999</v>
+        <v>-0.7113419801999999</v>
       </c>
       <c r="P92">
-        <v>-1.717771302</v>
+        <v>-1.7415613998</v>
       </c>
       <c r="Q92">
-        <v>-1.707771302</v>
+        <v>-1.7315613998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.323636744009412</v>
+        <v>1.465618604454903</v>
       </c>
       <c r="T92">
-        <v>7.815090455210514</v>
+        <v>8.683433839122795</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05733845701130324</v>
+        <v>0.0567083640771131</v>
       </c>
       <c r="W92">
-        <v>0.2222795918367347</v>
+        <v>0.2224281677506167</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.197718817280356</v>
+        <v>0.1955460830245279</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3343153070540025</v>
+        <v>0.3362153070540025</v>
       </c>
       <c r="C93">
-        <v>-6.016964300027228</v>
+        <v>-6.202107340549964</v>
       </c>
       <c r="D93">
-        <v>6.579135699972771</v>
+        <v>6.536092659450036</v>
       </c>
       <c r="E93">
-        <v>11.4211</v>
+        <v>11.5632</v>
       </c>
       <c r="F93">
-        <v>12.9311</v>
+        <v>13.0732</v>
       </c>
       <c r="G93">
         <v>0.335</v>
@@ -8907,37 +8907,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M93">
-        <v>3.04915338</v>
+        <v>3.08266056</v>
       </c>
       <c r="N93">
-        <v>-2.45290338</v>
+        <v>-2.48641056</v>
       </c>
       <c r="O93">
-        <v>-0.7113419801999999</v>
+        <v>-0.7210590624000001</v>
       </c>
       <c r="P93">
-        <v>-1.7415613998</v>
+        <v>-1.7653514976</v>
       </c>
       <c r="Q93">
-        <v>-1.7315613998</v>
+        <v>-1.7553514976</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.465618604454903</v>
+        <v>1.643095930011766</v>
       </c>
       <c r="T93">
-        <v>8.683433839122795</v>
+        <v>9.768863069013147</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0567083640771131</v>
+        <v>0.05609196881540533</v>
       </c>
       <c r="W93">
-        <v>0.2224281677506167</v>
+        <v>0.2225735137533274</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1955460830245279</v>
+        <v>0.1934205821220873</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3362153070540025</v>
+        <v>0.3381153070540024</v>
       </c>
       <c r="C94">
-        <v>-6.202107340549964</v>
+        <v>-6.386690836122299</v>
       </c>
       <c r="D94">
-        <v>6.536092659450036</v>
+        <v>6.4936091638777</v>
       </c>
       <c r="E94">
-        <v>11.5632</v>
+        <v>11.7053</v>
       </c>
       <c r="F94">
-        <v>13.0732</v>
+        <v>13.2153</v>
       </c>
       <c r="G94">
         <v>0.335</v>
@@ -8989,37 +8989,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M94">
-        <v>3.08266056</v>
+        <v>3.11616774</v>
       </c>
       <c r="N94">
-        <v>-2.48641056</v>
+        <v>-2.51991774</v>
       </c>
       <c r="O94">
-        <v>-0.7210590624000001</v>
+        <v>-0.7307761446</v>
       </c>
       <c r="P94">
-        <v>-1.7653514976</v>
+        <v>-1.7891415954</v>
       </c>
       <c r="Q94">
-        <v>-1.7553514976</v>
+        <v>-1.7791415954</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.643095930011766</v>
+        <v>1.87128106287059</v>
       </c>
       <c r="T94">
-        <v>9.768863069013147</v>
+        <v>11.16441493601503</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05609196881540533</v>
+        <v>0.05548882936577734</v>
       </c>
       <c r="W94">
-        <v>0.2225735137533274</v>
+        <v>0.2227157340355497</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1934205821220873</v>
+        <v>0.1913407909164736</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3381153070540024</v>
+        <v>0.3400153070540024</v>
       </c>
       <c r="C95">
-        <v>-6.386690836122299</v>
+        <v>-6.570725627125893</v>
       </c>
       <c r="D95">
-        <v>6.4936091638777</v>
+        <v>6.451674372874107</v>
       </c>
       <c r="E95">
-        <v>11.7053</v>
+        <v>11.8474</v>
       </c>
       <c r="F95">
-        <v>13.2153</v>
+        <v>13.3574</v>
       </c>
       <c r="G95">
         <v>0.335</v>
@@ -9071,37 +9071,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M95">
-        <v>3.11616774</v>
+        <v>3.14967492</v>
       </c>
       <c r="N95">
-        <v>-2.51991774</v>
+        <v>-2.55342492</v>
       </c>
       <c r="O95">
-        <v>-0.7307761446</v>
+        <v>-0.7404932268000001</v>
       </c>
       <c r="P95">
-        <v>-1.7891415954</v>
+        <v>-1.8129316932</v>
       </c>
       <c r="Q95">
-        <v>-1.7791415954</v>
+        <v>-1.8029316932</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.87128106287059</v>
+        <v>2.175527906682355</v>
       </c>
       <c r="T95">
-        <v>11.16441493601503</v>
+        <v>13.0251507586842</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05548882936577734</v>
+        <v>0.05489852267039672</v>
       </c>
       <c r="W95">
-        <v>0.2227157340355497</v>
+        <v>0.2228549283543205</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1913407909164736</v>
+        <v>0.1893052505875749</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3400153070540024</v>
+        <v>0.3419153070540024</v>
       </c>
       <c r="C96">
-        <v>-6.570725627125893</v>
+        <v>-6.754222275716656</v>
       </c>
       <c r="D96">
-        <v>6.451674372874107</v>
+        <v>6.410277724283343</v>
       </c>
       <c r="E96">
-        <v>11.8474</v>
+        <v>11.9895</v>
       </c>
       <c r="F96">
-        <v>13.3574</v>
+        <v>13.4995</v>
       </c>
       <c r="G96">
         <v>0.335</v>
@@ -9153,37 +9153,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M96">
-        <v>3.14967492</v>
+        <v>3.1831821</v>
       </c>
       <c r="N96">
-        <v>-2.55342492</v>
+        <v>-2.5869321</v>
       </c>
       <c r="O96">
-        <v>-0.7404932268000001</v>
+        <v>-0.7502103089999999</v>
       </c>
       <c r="P96">
-        <v>-1.8129316932</v>
+        <v>-1.836721791</v>
       </c>
       <c r="Q96">
-        <v>-1.8029316932</v>
+        <v>-1.826721791</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.175527906682355</v>
+        <v>2.601473488018828</v>
       </c>
       <c r="T96">
-        <v>13.0251507586842</v>
+        <v>15.63018091042105</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05489852267039672</v>
+        <v>0.05432064348439254</v>
       </c>
       <c r="W96">
-        <v>0.2228549283543205</v>
+        <v>0.2229911922663802</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1893052505875749</v>
+        <v>0.1873125637392846</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3419153070540024</v>
+        <v>0.3438153070540024</v>
       </c>
       <c r="C97">
-        <v>-6.754222275716656</v>
+        <v>-6.937191074693925</v>
       </c>
       <c r="D97">
-        <v>6.410277724283343</v>
+        <v>6.369408925306075</v>
       </c>
       <c r="E97">
-        <v>11.9895</v>
+        <v>12.1316</v>
       </c>
       <c r="F97">
-        <v>13.4995</v>
+        <v>13.6416</v>
       </c>
       <c r="G97">
         <v>0.335</v>
@@ -9235,37 +9235,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M97">
-        <v>3.1831821</v>
+        <v>3.21668928</v>
       </c>
       <c r="N97">
-        <v>-2.5869321</v>
+        <v>-2.62043928</v>
       </c>
       <c r="O97">
-        <v>-0.7502103089999999</v>
+        <v>-0.7599273912</v>
       </c>
       <c r="P97">
-        <v>-1.836721791</v>
+        <v>-1.8605118888</v>
       </c>
       <c r="Q97">
-        <v>-1.826721791</v>
+        <v>-1.8505118888</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.601473488018828</v>
+        <v>3.240391860023537</v>
       </c>
       <c r="T97">
-        <v>15.63018091042105</v>
+        <v>19.53772613802632</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05432064348439254</v>
+        <v>0.05375480344809679</v>
       </c>
       <c r="W97">
-        <v>0.2229911922663802</v>
+        <v>0.2231246173469388</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1873125637392846</v>
+        <v>0.1853613912003338</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3438153070540024</v>
+        <v>0.3457153070540024</v>
       </c>
       <c r="C98">
-        <v>-6.937191074693923</v>
+        <v>-7.119642056032472</v>
       </c>
       <c r="D98">
-        <v>6.369408925306075</v>
+        <v>6.329057943967526</v>
       </c>
       <c r="E98">
-        <v>12.1316</v>
+        <v>12.2737</v>
       </c>
       <c r="F98">
-        <v>13.6416</v>
+        <v>13.7837</v>
       </c>
       <c r="G98">
         <v>0.335</v>
@@ -9317,37 +9317,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M98">
-        <v>3.21668928</v>
+        <v>3.25019646</v>
       </c>
       <c r="N98">
-        <v>-2.62043928</v>
+        <v>-2.65394646</v>
       </c>
       <c r="O98">
-        <v>-0.7599273911999999</v>
+        <v>-0.7696444733999999</v>
       </c>
       <c r="P98">
-        <v>-1.8605118888</v>
+        <v>-1.8843019866</v>
       </c>
       <c r="Q98">
-        <v>-1.8505118888</v>
+        <v>-1.8743019866</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.240391860023528</v>
+        <v>4.305255813364704</v>
       </c>
       <c r="T98">
-        <v>19.53772613802627</v>
+        <v>26.05030151736836</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05375480344809679</v>
+        <v>0.05320063021667312</v>
       </c>
       <c r="W98">
-        <v>0.2231246173469388</v>
+        <v>0.2232552913949085</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1853613912003338</v>
+        <v>0.1834504490230108</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3457153070540024</v>
+        <v>0.3476153070540025</v>
       </c>
       <c r="C99">
-        <v>-7.119642056032472</v>
+        <v>-7.301584999092306</v>
       </c>
       <c r="D99">
-        <v>6.329057943967526</v>
+        <v>6.289215000907693</v>
       </c>
       <c r="E99">
-        <v>12.2737</v>
+        <v>12.4158</v>
       </c>
       <c r="F99">
-        <v>13.7837</v>
+        <v>13.9258</v>
       </c>
       <c r="G99">
         <v>0.335</v>
@@ -9399,37 +9399,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M99">
-        <v>3.25019646</v>
+        <v>3.28370364</v>
       </c>
       <c r="N99">
-        <v>-2.65394646</v>
+        <v>-2.68745364</v>
       </c>
       <c r="O99">
-        <v>-0.7696444733999999</v>
+        <v>-0.7793615555999999</v>
       </c>
       <c r="P99">
-        <v>-1.8843019866</v>
+        <v>-1.9080920844</v>
       </c>
       <c r="Q99">
-        <v>-1.8743019866</v>
+        <v>-1.8980920844</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.305255813364704</v>
+        <v>6.434983720047056</v>
       </c>
       <c r="T99">
-        <v>26.05030151736836</v>
+        <v>39.07545227605254</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05320063021667312</v>
+        <v>0.05265776664303359</v>
       </c>
       <c r="W99">
-        <v>0.2232552913949085</v>
+        <v>0.2233832986255727</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1834504490230108</v>
+        <v>0.181578505665633</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3476153070540025</v>
+        <v>0.3495153070540025</v>
       </c>
       <c r="C100">
-        <v>-7.301584999092306</v>
+        <v>-7.483029438520245</v>
       </c>
       <c r="D100">
-        <v>6.289215000907693</v>
+        <v>6.249870561479753</v>
       </c>
       <c r="E100">
-        <v>12.4158</v>
+        <v>12.5579</v>
       </c>
       <c r="F100">
-        <v>13.9258</v>
+        <v>14.0679</v>
       </c>
       <c r="G100">
         <v>0.335</v>
@@ -9481,37 +9481,37 @@
         <v>0.5962499999999999</v>
       </c>
       <c r="M100">
-        <v>3.28370364</v>
+        <v>3.31721082</v>
       </c>
       <c r="N100">
-        <v>-2.68745364</v>
+        <v>-2.72096082</v>
       </c>
       <c r="O100">
-        <v>-0.7793615555999999</v>
+        <v>-0.7890786377999999</v>
       </c>
       <c r="P100">
-        <v>-1.9080920844</v>
+        <v>-1.9318821822</v>
       </c>
       <c r="Q100">
-        <v>-1.8980920844</v>
+        <v>-1.9218821822</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>6.434983720047056</v>
+        <v>12.82416744009411</v>
       </c>
       <c r="T100">
-        <v>39.07545227605254</v>
+        <v>78.15090455210508</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05265776664303359</v>
+        <v>0.05212587001027568</v>
       </c>
       <c r="W100">
-        <v>0.2233832986255727</v>
+        <v>0.223508719851577</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.181578505665633</v>
+        <v>0.1797443793457782</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3495153070540025</v>
-      </c>
-      <c r="C101">
-        <v>-7.483029438520245</v>
-      </c>
-      <c r="D101">
-        <v>6.249870561479753</v>
-      </c>
-      <c r="E101">
-        <v>12.5579</v>
-      </c>
-      <c r="F101">
-        <v>14.0679</v>
-      </c>
-      <c r="G101">
-        <v>0.335</v>
-      </c>
-      <c r="H101">
-        <v>12.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.60625</v>
-      </c>
-      <c r="K101">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0.5962499999999999</v>
-      </c>
-      <c r="M101">
-        <v>3.31721082</v>
-      </c>
-      <c r="N101">
-        <v>-2.72096082</v>
-      </c>
-      <c r="O101">
-        <v>-0.7890786377999999</v>
-      </c>
-      <c r="P101">
-        <v>-1.9318821822</v>
-      </c>
-      <c r="Q101">
-        <v>-1.9218821822</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>12.82416744009411</v>
-      </c>
-      <c r="T101">
-        <v>78.15090455210508</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05212587001027568</v>
-      </c>
-      <c r="W101">
-        <v>0.223508719851577</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1797443793457782</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
